--- a/alliance-mobilization.xlsx
+++ b/alliance-mobilization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\SynologyDrive\dgefers\Desktop\Rise of Kingdoms\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164203D2-4F7E-46B3-92FB-1E91196AD57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F94EDC-7C37-4118-9FD8-34F78BFA3188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{909B3E3F-35C1-45D2-894E-8B07AC82B732}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{909B3E3F-35C1-45D2-894E-8B07AC82B732}"/>
   </bookViews>
   <sheets>
     <sheet name="November 2025" sheetId="1" r:id="rId1"/>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="382">
   <si>
     <t>Start</t>
   </si>
@@ -994,9 +994,6 @@
     <t>Kursord</t>
   </si>
   <si>
-    <t>SEMIHBZ14</t>
-  </si>
-  <si>
     <t>CihangirTR farm</t>
   </si>
   <si>
@@ -1013,9 +1010,6 @@
   </si>
   <si>
     <t>świoniu farm</t>
-  </si>
-  <si>
-    <t>PLTubylec</t>
   </si>
   <si>
     <t>Tubylec</t>
@@ -1346,9 +1340,6 @@
     <t>WiedźmiN F10</t>
   </si>
   <si>
-    <t>ThaoLy F2P</t>
-  </si>
-  <si>
     <t>Tubylec Rss012</t>
   </si>
   <si>
@@ -1377,6 +1368,12 @@
   </si>
   <si>
     <t>✗ Ares ✗ (Aresツ)</t>
+  </si>
+  <si>
+    <t>ThaoLy F2P (Duweiii)</t>
+  </si>
+  <si>
+    <t>ANS FARMأ (ANS أ)</t>
   </si>
 </sst>
 </file>
@@ -1567,6 +1564,105 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="151">
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1874,21 +1970,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1897,10 +1978,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1917,6 +1994,14 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1933,10 +2018,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1945,24 +2026,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2009,21 +2072,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2032,10 +2080,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2052,6 +2096,14 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2068,10 +2120,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2080,24 +2128,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2877,21 +2907,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2900,10 +2915,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2920,6 +2931,14 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2936,10 +2955,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2948,24 +2963,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3121,18 +3118,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}" name="AllianceMobilizationNovember2025" displayName="AllianceMobilizationNovember2025" ref="B12:G157" totalsRowCount="1" headerRowDxfId="128" dataDxfId="127" totalsRowDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}" name="AllianceMobilizationNovember2025" displayName="AllianceMobilizationNovember2025" ref="B12:G157" totalsRowCount="1" headerRowDxfId="134" dataDxfId="133" totalsRowDxfId="132">
   <autoFilter ref="B12:G156" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G156">
     <sortCondition ref="B12:B156"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E80EFDDD-CF56-40E0-84FA-EE7D9422EE02}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{3B6633FB-4D7C-4AE3-BAB1-89D7B440BAB2}" name="Governor" dataDxfId="123" totalsRowDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{C9B4BB00-6F72-49A1-BC67-75C7DBA56D12}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="121" totalsRowDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{495DCF47-EE1A-43FF-BC77-24F1998BD592}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="119" totalsRowDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{5DA3BDD5-5ED1-4533-9FF2-9EA9C5A6505D}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="117" totalsRowDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{695CA109-E314-447D-8CC9-1DE4EBE1D106}" name="Points per_x000a_Quest compl." dataDxfId="115" totalsRowDxfId="114">
+    <tableColumn id="1" xr3:uid="{E80EFDDD-CF56-40E0-84FA-EE7D9422EE02}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="131" totalsRowDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{3B6633FB-4D7C-4AE3-BAB1-89D7B440BAB2}" name="Governor" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{C9B4BB00-6F72-49A1-BC67-75C7DBA56D12}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{495DCF47-EE1A-43FF-BC77-24F1998BD592}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="5" xr3:uid="{5DA3BDD5-5ED1-4533-9FF2-9EA9C5A6505D}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="6" xr3:uid="{695CA109-E314-447D-8CC9-1DE4EBE1D106}" name="Points per_x000a_Quest compl." dataDxfId="121" totalsRowDxfId="120">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3141,18 +3138,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4C009E5-0657-4DF1-ADEB-1771FC5393CD}" name="AllianceMobilizationJanuary2026" displayName="AllianceMobilizationJanuary2026" ref="B12:G124" totalsRowCount="1" headerRowDxfId="113" dataDxfId="112" totalsRowDxfId="111">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4C009E5-0657-4DF1-ADEB-1771FC5393CD}" name="AllianceMobilizationJanuary2026" displayName="AllianceMobilizationJanuary2026" ref="B12:G124" totalsRowCount="1" headerRowDxfId="119" dataDxfId="118" totalsRowDxfId="117">
   <autoFilter ref="B12:G123" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G123">
     <sortCondition ref="B12:B123"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2E23F4F9-51DB-40ED-9226-3A3B014E70A6}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="110" totalsRowDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{8F7C649B-6D88-4F11-B796-32F33F442642}" name="Governor" dataDxfId="108" totalsRowDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{2193B9C7-6D26-4A08-B094-729B3B441B48}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{E4294EBA-4938-464A-8060-8F7F2F839DBE}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="104" totalsRowDxfId="103"/>
-    <tableColumn id="5" xr3:uid="{7FB251BF-169C-4924-83A6-069E02C7F5D2}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="102" totalsRowDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{EBF17B55-1711-466D-8489-61F0248BF567}" name="Points per_x000a_Quest compl." dataDxfId="100" totalsRowDxfId="99">
+    <tableColumn id="1" xr3:uid="{2E23F4F9-51DB-40ED-9226-3A3B014E70A6}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{8F7C649B-6D88-4F11-B796-32F33F442642}" name="Governor" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="3" xr3:uid="{2193B9C7-6D26-4A08-B094-729B3B441B48}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="4" xr3:uid="{E4294EBA-4938-464A-8060-8F7F2F839DBE}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{7FB251BF-169C-4924-83A6-069E02C7F5D2}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="107"/>
+    <tableColumn id="6" xr3:uid="{EBF17B55-1711-466D-8489-61F0248BF567}" name="Points per_x000a_Quest compl." dataDxfId="106" totalsRowDxfId="105">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3161,18 +3158,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1D3B8002-176C-472A-94EF-BAA86E82E885}" name="AllianceMobilizationFebruary2026" displayName="AllianceMobilizationFebruary2026" ref="B12:G152" totalsRowCount="1" headerRowDxfId="98" dataDxfId="97" totalsRowDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1D3B8002-176C-472A-94EF-BAA86E82E885}" name="AllianceMobilizationFebruary2026" displayName="AllianceMobilizationFebruary2026" ref="B12:G152" totalsRowCount="1" headerRowDxfId="104" dataDxfId="103" totalsRowDxfId="102">
   <autoFilter ref="B12:G151" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G151">
     <sortCondition ref="B12:B151"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{B30EAC76-060F-4B49-90A4-959A62E0C548}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="95" totalsRowDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{06F94D66-C61F-4063-9650-9472D99D94DB}" name="Governor" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{6671FE25-D716-415E-9CC6-0747DC95F98D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{7F3CD8A8-5FB7-494E-8C4D-D884901E7CAD}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{F7D5B1B8-846B-4525-BFE2-0E221E02DD5B}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{9BAA2795-21A9-4C74-AECE-58FD09C05E9B}" name="Points per_x000a_Quest compl." dataDxfId="85" totalsRowDxfId="84">
+    <tableColumn id="1" xr3:uid="{B30EAC76-060F-4B49-90A4-959A62E0C548}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{06F94D66-C61F-4063-9650-9472D99D94DB}" name="Governor" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{6671FE25-D716-415E-9CC6-0747DC95F98D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{7F3CD8A8-5FB7-494E-8C4D-D884901E7CAD}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94"/>
+    <tableColumn id="5" xr3:uid="{F7D5B1B8-846B-4525-BFE2-0E221E02DD5B}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{9BAA2795-21A9-4C74-AECE-58FD09C05E9B}" name="Points per_x000a_Quest compl." dataDxfId="91" totalsRowDxfId="90">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3181,18 +3178,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E01E6D77-4F29-4434-85C0-E3884F5E01CB}" name="AllianceMobilizationMarch2026" displayName="AllianceMobilizationMarch2026" ref="B12:G145" totalsRowCount="1" headerRowDxfId="83" dataDxfId="82" totalsRowDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E01E6D77-4F29-4434-85C0-E3884F5E01CB}" name="AllianceMobilizationMarch2026" displayName="AllianceMobilizationMarch2026" ref="B12:G145" totalsRowCount="1" headerRowDxfId="89" dataDxfId="88" totalsRowDxfId="87">
   <autoFilter ref="B12:G144" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G144">
     <sortCondition ref="B12:B144"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8F1B437D-7DC7-4032-B373-39501AAC305A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="80" totalsRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{5748D8F1-4EB7-49DC-9F19-02F8544ADB80}" name="Governor" dataDxfId="79" totalsRowDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{C16FF4F5-BE34-45C7-AC36-B2C513C2BD38}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{E81DD37D-FD17-4F66-B511-74896A7F0F2A}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="77" totalsRowDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{DC35B835-A19A-439D-893B-122792042439}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{1621615B-84A5-4D0B-B67B-14F5B8B6075A}" name="Points per_x000a_Quest compl." dataDxfId="75" totalsRowDxfId="6">
+    <tableColumn id="1" xr3:uid="{8F1B437D-7DC7-4032-B373-39501AAC305A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="86" totalsRowDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{5748D8F1-4EB7-49DC-9F19-02F8544ADB80}" name="Governor" dataDxfId="85" totalsRowDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C16FF4F5-BE34-45C7-AC36-B2C513C2BD38}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{E81DD37D-FD17-4F66-B511-74896A7F0F2A}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{DC35B835-A19A-439D-893B-122792042439}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{1621615B-84A5-4D0B-B67B-14F5B8B6075A}" name="Points per_x000a_Quest compl." dataDxfId="81" totalsRowDxfId="24">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3201,18 +3198,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ED8FBDF9-FCC7-4C93-9B38-43FF67FDEB9E}" name="AllianceMobilizationMarch2026678" displayName="AllianceMobilizationMarch2026678" ref="B12:G132" totalsRowCount="1" headerRowDxfId="74" dataDxfId="73" totalsRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ED8FBDF9-FCC7-4C93-9B38-43FF67FDEB9E}" name="AllianceMobilizationMarch2026678" displayName="AllianceMobilizationMarch2026678" ref="B12:G132" totalsRowCount="1" headerRowDxfId="80" dataDxfId="79" totalsRowDxfId="78">
   <autoFilter ref="B12:G131" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G131">
     <sortCondition ref="B12:B131"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D8E9B715-1D59-4A60-9E31-0B5FEE63A12A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="71" totalsRowDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{67F290D2-0820-48FE-BB36-118CF7DC1854}" name="Governor" dataDxfId="70" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{3D97C902-1962-42BB-BF4A-70FBB84A275D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="69" totalsRowDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6F4B57EE-DD44-4C31-991C-14DA6FAEE2CC}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{674F52CC-ADC3-4CFF-AF18-0C3EE0B6A778}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{7956BB13-96CA-4BA6-AE82-6C3911FEF104}" name="Points per_x000a_Quest compl." dataDxfId="66" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{D8E9B715-1D59-4A60-9E31-0B5FEE63A12A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{67F290D2-0820-48FE-BB36-118CF7DC1854}" name="Governor" dataDxfId="76" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{3D97C902-1962-42BB-BF4A-70FBB84A275D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6F4B57EE-DD44-4C31-991C-14DA6FAEE2CC}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{674F52CC-ADC3-4CFF-AF18-0C3EE0B6A778}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="73" totalsRowDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{7956BB13-96CA-4BA6-AE82-6C3911FEF104}" name="Points per_x000a_Quest compl." dataDxfId="72" totalsRowDxfId="18">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3221,18 +3218,18 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C1877A37-602D-4929-A27F-182C37222BF1}" name="AllianceMobilizationMarch202667" displayName="AllianceMobilizationMarch202667" ref="B12:G153" totalsRowCount="1" headerRowDxfId="65" dataDxfId="64" totalsRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C1877A37-602D-4929-A27F-182C37222BF1}" name="AllianceMobilizationMarch202667" displayName="AllianceMobilizationMarch202667" ref="B12:G153" totalsRowCount="1" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
   <autoFilter ref="B12:G152" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G152">
     <sortCondition ref="B12:B152"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{024374DF-58D9-4D7E-A2F8-E94E3FDE62D4}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{63C21810-283C-483A-9B6F-5290EE4535DE}" name="Governor" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{32C633D8-BA68-4EF3-BDCF-75E0D0078BCA}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{D1311703-382D-425F-A173-91EEC303E293}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{0A4AC45F-A60F-4A6F-9A75-E0BCC22CB6F0}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{78CAC145-EDB3-425A-A337-3F1234C5B602}" name="Points per_x000a_Quest compl." dataDxfId="52" totalsRowDxfId="51">
+    <tableColumn id="1" xr3:uid="{024374DF-58D9-4D7E-A2F8-E94E3FDE62D4}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="68" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{63C21810-283C-483A-9B6F-5290EE4535DE}" name="Governor" dataDxfId="67" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{32C633D8-BA68-4EF3-BDCF-75E0D0078BCA}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{D1311703-382D-425F-A173-91EEC303E293}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{0A4AC45F-A60F-4A6F-9A75-E0BCC22CB6F0}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{78CAC145-EDB3-425A-A337-3F1234C5B602}" name="Points per_x000a_Quest compl." dataDxfId="63" totalsRowDxfId="0">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3241,18 +3238,18 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0E6F41ED-D120-45F9-8558-56F61F3BD8B0}" name="AllianceMobilizationMarch20266" displayName="AllianceMobilizationMarch20266" ref="B12:G150" totalsRowCount="1" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0E6F41ED-D120-45F9-8558-56F61F3BD8B0}" name="AllianceMobilizationMarch20266" displayName="AllianceMobilizationMarch20266" ref="B12:G150" totalsRowCount="1" headerRowDxfId="62" dataDxfId="61" totalsRowDxfId="60">
   <autoFilter ref="B12:G149" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G149">
     <sortCondition ref="B12:B149"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{50D3F7F9-6587-4E14-9172-32543B79C5F3}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{4BB8DE34-B1C7-4669-94D2-DFACA05ED05A}" name="Governor" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{4E94BDE2-12D0-4603-9BB3-91BDDE3B74F4}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{1390E1DB-6F54-4A1B-8886-BA8A8C22BB6D}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{0F97E3EF-FD9E-46CF-9FE4-6549B5704E98}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{9863C91B-4251-4CB7-BB1D-4FE464EF7779}" name="Points per_x000a_Quest compl." dataDxfId="37" totalsRowDxfId="36">
+    <tableColumn id="1" xr3:uid="{50D3F7F9-6587-4E14-9172-32543B79C5F3}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="59" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{4BB8DE34-B1C7-4669-94D2-DFACA05ED05A}" name="Governor" dataDxfId="58" totalsRowDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4E94BDE2-12D0-4603-9BB3-91BDDE3B74F4}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{1390E1DB-6F54-4A1B-8886-BA8A8C22BB6D}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{0F97E3EF-FD9E-46CF-9FE4-6549B5704E98}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{9863C91B-4251-4CB7-BB1D-4FE464EF7779}" name="Points per_x000a_Quest compl." dataDxfId="54" totalsRowDxfId="12">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3267,12 +3264,12 @@
     <sortCondition ref="B12:B146"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0BD6F31C-88ED-4F5D-B312-0E80EA472799}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="140" totalsRowDxfId="139"/>
-    <tableColumn id="2" xr3:uid="{5476817D-6BB2-4219-BAAC-93030D81F834}" name="Governor" dataDxfId="138" totalsRowDxfId="137"/>
-    <tableColumn id="3" xr3:uid="{2F5807B0-B0CD-4270-8190-6228514D5EB9}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="135"/>
-    <tableColumn id="4" xr3:uid="{66A94722-A980-4C21-AD3A-4DE5F6442EE7}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="134" totalsRowDxfId="133"/>
-    <tableColumn id="5" xr3:uid="{FA7AC61E-5D38-40A4-AFEF-2DF13BCBF7BB}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="132" totalsRowDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{8CB484E1-EBED-4CF2-A72C-F49F44A142FD}" name="Points per_x000a_Quest compl." dataDxfId="130" totalsRowDxfId="129">
+    <tableColumn id="1" xr3:uid="{0BD6F31C-88ED-4F5D-B312-0E80EA472799}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="140" totalsRowDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{5476817D-6BB2-4219-BAAC-93030D81F834}" name="Governor" dataDxfId="139" totalsRowDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{2F5807B0-B0CD-4270-8190-6228514D5EB9}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="138" totalsRowDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{66A94722-A980-4C21-AD3A-4DE5F6442EE7}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="137" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{FA7AC61E-5D38-40A4-AFEF-2DF13BCBF7BB}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8CB484E1-EBED-4CF2-A72C-F49F44A142FD}" name="Points per_x000a_Quest compl." dataDxfId="135" totalsRowDxfId="6">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3703,7 +3700,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -7367,13 +7364,13 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D156">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7493,7 +7490,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -10332,13 +10329,13 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D123">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10461,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -13999,13 +13996,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D151">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14129,7 +14126,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -17493,13 +17490,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D144">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17528,7 +17525,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -17553,7 +17550,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17562,7 +17559,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17580,7 +17577,7 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H7" s="19"/>
     </row>
@@ -17599,7 +17596,7 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17624,7 +17621,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -17642,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D13" s="14">
         <v>6820</v>
@@ -17667,7 +17664,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D14" s="14">
         <v>6200</v>
@@ -17692,7 +17689,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D15" s="14">
         <v>5400</v>
@@ -17717,7 +17714,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D16" s="14">
         <v>5380</v>
@@ -17742,7 +17739,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D17" s="14">
         <v>5340</v>
@@ -17767,7 +17764,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" s="14">
         <v>5260</v>
@@ -17792,7 +17789,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D19" s="14">
         <v>5210</v>
@@ -17842,7 +17839,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D21" s="14">
         <v>4660</v>
@@ -17967,7 +17964,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D26" s="14">
         <v>3940</v>
@@ -17992,7 +17989,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D27" s="14">
         <v>3820</v>
@@ -18092,7 +18089,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D31" s="14">
         <v>3490</v>
@@ -18192,7 +18189,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D35" s="14">
         <v>3150</v>
@@ -18267,7 +18264,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D38" s="14">
         <v>3040</v>
@@ -18317,7 +18314,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D40" s="14">
         <v>3000</v>
@@ -18442,7 +18439,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D45" s="14">
         <v>2750</v>
@@ -18467,7 +18464,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D46" s="14">
         <v>2740</v>
@@ -18517,7 +18514,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D48" s="14">
         <v>2720</v>
@@ -18692,7 +18689,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D55" s="14">
         <v>2610</v>
@@ -18717,7 +18714,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D56" s="14">
         <v>2600</v>
@@ -18742,7 +18739,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D57" s="14">
         <v>2600</v>
@@ -18792,7 +18789,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D59" s="14">
         <v>2540</v>
@@ -18892,7 +18889,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D63" s="14">
         <v>2500</v>
@@ -18942,7 +18939,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="D65" s="14">
         <v>2460</v>
@@ -19067,7 +19064,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="D70" s="14">
         <v>2360</v>
@@ -19142,7 +19139,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D73" s="14">
         <v>2320</v>
@@ -19167,7 +19164,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D74" s="14">
         <v>2320</v>
@@ -19242,7 +19239,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D77" s="14">
         <v>2300</v>
@@ -19292,7 +19289,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D79" s="14">
         <v>2270</v>
@@ -19367,7 +19364,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D82" s="14">
         <v>2240</v>
@@ -19417,7 +19414,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D84" s="14">
         <v>2180</v>
@@ -19442,7 +19439,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" s="14">
         <v>2180</v>
@@ -19492,7 +19489,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D87" s="14">
         <v>2160</v>
@@ -19542,7 +19539,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D89" s="14">
         <v>2100</v>
@@ -19592,7 +19589,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D91" s="14">
         <v>2080</v>
@@ -19617,7 +19614,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D92" s="14">
         <v>2080</v>
@@ -19667,7 +19664,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D94" s="14">
         <v>2080</v>
@@ -19742,7 +19739,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D97" s="14">
         <v>2060</v>
@@ -19792,7 +19789,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D99" s="14">
         <v>2060</v>
@@ -19817,7 +19814,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D100" s="14">
         <v>2050</v>
@@ -19867,7 +19864,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D102" s="14">
         <v>2040</v>
@@ -19992,7 +19989,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D107" s="14">
         <v>2000</v>
@@ -20017,7 +20014,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D108" s="14">
         <v>2000</v>
@@ -20042,7 +20039,7 @@
         <v>97</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D109" s="14">
         <v>1920</v>
@@ -20067,7 +20064,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D110" s="14">
         <v>1900</v>
@@ -20142,7 +20139,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D113" s="14">
         <v>1750</v>
@@ -20242,7 +20239,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D117" s="14">
         <v>1540</v>
@@ -20342,7 +20339,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D121" s="14">
         <v>1320</v>
@@ -20367,7 +20364,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D122" s="14">
         <v>1320</v>
@@ -20392,7 +20389,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D123" s="14">
         <v>1060</v>
@@ -20442,7 +20439,7 @@
         <v>113</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D125" s="14">
         <v>930</v>
@@ -20467,7 +20464,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D126" s="14">
         <v>660</v>
@@ -20492,7 +20489,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D127" s="14">
         <v>260</v>
@@ -20517,7 +20514,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D128" s="14">
         <v>0</v>
@@ -20592,7 +20589,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D131" s="14">
         <v>0</v>
@@ -20663,13 +20660,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D131">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20698,7 +20695,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -20723,7 +20720,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -20732,7 +20729,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -20750,7 +20747,7 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H7" s="19"/>
     </row>
@@ -20794,7 +20791,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -20837,7 +20834,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D14" s="14">
         <v>5230</v>
@@ -20862,7 +20859,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D15" s="14">
         <v>4450</v>
@@ -21112,7 +21109,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D25" s="14">
         <v>3580</v>
@@ -21187,7 +21184,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D28" s="14">
         <v>3540</v>
@@ -21237,7 +21234,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D30" s="14">
         <v>3360</v>
@@ -21312,7 +21309,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D33" s="14">
         <v>3120</v>
@@ -21337,7 +21334,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D34" s="14">
         <v>3080</v>
@@ -21362,7 +21359,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D35" s="14">
         <v>3060</v>
@@ -21387,7 +21384,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D36" s="14">
         <v>3060</v>
@@ -21462,7 +21459,7 @@
         <v>27</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D39" s="14">
         <v>2940</v>
@@ -21562,7 +21559,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D43" s="14">
         <v>2830</v>
@@ -21612,7 +21609,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D45" s="14">
         <v>2780</v>
@@ -21762,7 +21759,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D51" s="14">
         <v>2620</v>
@@ -21787,7 +21784,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D52" s="14">
         <v>2600</v>
@@ -21812,7 +21809,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D53" s="14">
         <v>2600</v>
@@ -21862,7 +21859,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D55" s="14">
         <v>2580</v>
@@ -21887,7 +21884,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D56" s="14">
         <v>2580</v>
@@ -21937,7 +21934,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D58" s="14">
         <v>2440</v>
@@ -21987,7 +21984,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D60" s="14">
         <v>2410</v>
@@ -22037,7 +22034,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D62" s="14">
         <v>2340</v>
@@ -22162,7 +22159,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D67" s="14">
         <v>2240</v>
@@ -22187,7 +22184,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D68" s="14">
         <v>2240</v>
@@ -22287,7 +22284,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D72" s="14">
         <v>2200</v>
@@ -22462,7 +22459,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D79" s="14">
         <v>2080</v>
@@ -22487,7 +22484,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D80" s="14">
         <v>2070</v>
@@ -22512,7 +22509,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D81" s="14">
         <v>2060</v>
@@ -22587,7 +22584,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D84" s="14">
         <v>2020</v>
@@ -22612,7 +22609,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D85" s="14">
         <v>2020</v>
@@ -22687,7 +22684,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D88" s="14">
         <v>1970</v>
@@ -22712,7 +22709,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D89" s="14">
         <v>1970</v>
@@ -22737,7 +22734,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D90" s="14">
         <v>1970</v>
@@ -22762,7 +22759,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D91" s="14">
         <v>1940</v>
@@ -22787,7 +22784,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D92" s="14">
         <v>1930</v>
@@ -22837,7 +22834,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D94" s="14">
         <v>1920</v>
@@ -22987,7 +22984,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D100" s="14">
         <v>1870</v>
@@ -23062,7 +23059,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D103" s="14">
         <v>1840</v>
@@ -23137,7 +23134,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D106" s="14">
         <v>1810</v>
@@ -23162,7 +23159,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D107" s="14">
         <v>1800</v>
@@ -23187,7 +23184,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D108" s="14">
         <v>1770</v>
@@ -23212,7 +23209,7 @@
         <v>97</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D109" s="14">
         <v>1740</v>
@@ -23237,7 +23234,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D110" s="14">
         <v>1730</v>
@@ -23262,7 +23259,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D111" s="14">
         <v>1700</v>
@@ -23287,7 +23284,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D112" s="14">
         <v>1650</v>
@@ -23312,7 +23309,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D113" s="14">
         <v>1620</v>
@@ -23362,7 +23359,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D115" s="14">
         <v>1600</v>
@@ -23462,7 +23459,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D119" s="14">
         <v>1100</v>
@@ -23487,7 +23484,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D120" s="14">
         <v>1040</v>
@@ -23512,7 +23509,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D121" s="14">
         <v>980</v>
@@ -23537,7 +23534,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D122" s="14">
         <v>920</v>
@@ -23562,7 +23559,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D123" s="14">
         <v>850</v>
@@ -23587,7 +23584,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D124" s="14">
         <v>850</v>
@@ -23637,7 +23634,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D126" s="14">
         <v>690</v>
@@ -23662,7 +23659,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D127" s="14">
         <v>660</v>
@@ -23712,7 +23709,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D129" s="14">
         <v>560</v>
@@ -23737,7 +23734,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D130" s="14">
         <v>510</v>
@@ -23762,7 +23759,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D131" s="14">
         <v>480</v>
@@ -23787,7 +23784,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D132" s="14">
         <v>240</v>
@@ -23812,7 +23809,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D133" s="14">
         <v>240</v>
@@ -23837,7 +23834,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D134" s="14">
         <v>230</v>
@@ -23862,7 +23859,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D135" s="14">
         <v>200</v>
@@ -23912,7 +23909,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="D137" s="14">
         <v>180</v>
@@ -23937,7 +23934,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D138" s="14">
         <v>150</v>
@@ -23962,7 +23959,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -23987,7 +23984,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D140" s="14">
         <v>0</v>
@@ -24012,7 +24009,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D141" s="14">
         <v>0</v>
@@ -24037,7 +24034,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D142" s="14">
         <v>0</v>
@@ -24062,7 +24059,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -24087,7 +24084,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -24112,7 +24109,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -24162,7 +24159,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D147" s="14">
         <v>0</v>
@@ -24187,7 +24184,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D148" s="14">
         <v>0</v>
@@ -24212,7 +24209,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D149" s="14">
         <v>0</v>
@@ -24262,7 +24259,7 @@
         <v>139</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D151" s="14">
         <v>0</v>
@@ -24287,7 +24284,7 @@
         <v>140</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D152" s="14">
         <v>0</v>
@@ -24358,13 +24355,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D152">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24393,7 +24390,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -24489,7 +24486,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -24557,7 +24554,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="D15" s="14">
         <v>5020</v>
@@ -24582,7 +24579,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D16" s="14">
         <v>4830</v>
@@ -24707,7 +24704,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D21" s="14">
         <v>4060</v>
@@ -24882,7 +24879,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D28" s="14">
         <v>3260</v>
@@ -24907,7 +24904,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D29" s="14">
         <v>3140</v>
@@ -25007,7 +25004,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D33" s="14">
         <v>2940</v>
@@ -25057,7 +25054,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D35" s="14">
         <v>2850</v>
@@ -25082,7 +25079,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="D36" s="14">
         <v>2810</v>
@@ -25107,7 +25104,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D37" s="14">
         <v>2800</v>
@@ -25257,7 +25254,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D43" s="14">
         <v>2660</v>
@@ -25282,7 +25279,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D44" s="14">
         <v>2640</v>
@@ -25382,7 +25379,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D48" s="14">
         <v>2580</v>
@@ -25482,7 +25479,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D52" s="14">
         <v>2480</v>
@@ -25557,7 +25554,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D55" s="14">
         <v>2420</v>
@@ -25582,7 +25579,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D56" s="14">
         <v>2420</v>
@@ -25607,7 +25604,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D57" s="14">
         <v>2390</v>
@@ -25632,7 +25629,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D58" s="14">
         <v>2380</v>
@@ -25682,7 +25679,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D60" s="14">
         <v>2380</v>
@@ -25707,7 +25704,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D61" s="14">
         <v>2370</v>
@@ -25732,7 +25729,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D62" s="14">
         <v>2360</v>
@@ -25757,7 +25754,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D63" s="14">
         <v>2340</v>
@@ -25857,7 +25854,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D67" s="14">
         <v>2200</v>
@@ -25907,7 +25904,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D69" s="14">
         <v>2180</v>
@@ -25957,7 +25954,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D71" s="14">
         <v>2160</v>
@@ -26007,7 +26004,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D73" s="14">
         <v>2120</v>
@@ -26032,7 +26029,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D74" s="14">
         <v>2120</v>
@@ -26157,7 +26154,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D79" s="14">
         <v>2070</v>
@@ -26182,7 +26179,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D80" s="14">
         <v>2040</v>
@@ -26207,7 +26204,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D81" s="14">
         <v>2040</v>
@@ -26232,7 +26229,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D82" s="14">
         <v>2040</v>
@@ -26282,7 +26279,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D84" s="14">
         <v>2020</v>
@@ -26307,7 +26304,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D85" s="14">
         <v>2020</v>
@@ -26332,7 +26329,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D86" s="14">
         <v>2010</v>
@@ -26357,7 +26354,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D87" s="14">
         <v>2000</v>
@@ -26382,7 +26379,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D88" s="14">
         <v>2000</v>
@@ -26407,7 +26404,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D89" s="14">
         <v>1990</v>
@@ -26432,7 +26429,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D90" s="14">
         <v>1960</v>
@@ -26482,7 +26479,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D92" s="14">
         <v>1920</v>
@@ -26507,7 +26504,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D93" s="14">
         <v>1920</v>
@@ -26557,7 +26554,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D95" s="14">
         <v>1890</v>
@@ -26582,7 +26579,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D96" s="14">
         <v>1890</v>
@@ -26607,7 +26604,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D97" s="14">
         <v>1880</v>
@@ -26657,7 +26654,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D99" s="14">
         <v>1860</v>
@@ -26732,7 +26729,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D102" s="14">
         <v>1820</v>
@@ -26757,7 +26754,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D103" s="14">
         <v>1820</v>
@@ -26807,7 +26804,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D105" s="14">
         <v>1800</v>
@@ -26832,7 +26829,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D106" s="14">
         <v>1800</v>
@@ -26882,7 +26879,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D108" s="14">
         <v>1770</v>
@@ -26932,7 +26929,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D110" s="14">
         <v>1700</v>
@@ -26957,7 +26954,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D111" s="14">
         <v>1530</v>
@@ -26982,7 +26979,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D112" s="14">
         <v>1510</v>
@@ -27007,7 +27004,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D113" s="14">
         <v>1480</v>
@@ -27057,7 +27054,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D115" s="14">
         <v>1180</v>
@@ -27082,7 +27079,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D116" s="14">
         <v>1180</v>
@@ -27107,7 +27104,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D117" s="14">
         <v>1140</v>
@@ -27132,7 +27129,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D118" s="14">
         <v>1130</v>
@@ -27157,7 +27154,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D119" s="14">
         <v>1100</v>
@@ -27207,7 +27204,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D121" s="14">
         <v>920</v>
@@ -27257,7 +27254,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D123" s="14">
         <v>810</v>
@@ -27282,7 +27279,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D124" s="14">
         <v>760</v>
@@ -27332,7 +27329,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D126" s="14">
         <v>360</v>
@@ -27357,7 +27354,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D127" s="14">
         <v>360</v>
@@ -27382,7 +27379,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D128" s="14">
         <v>220</v>
@@ -27407,7 +27404,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D129" s="14">
         <v>180</v>
@@ -27432,7 +27429,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D130" s="14">
         <v>180</v>
@@ -27457,7 +27454,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D131" s="14">
         <v>180</v>
@@ -27507,7 +27504,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D133" s="14">
         <v>0</v>
@@ -27532,7 +27529,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D134" s="14">
         <v>0</v>
@@ -27557,7 +27554,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D135" s="14">
         <v>0</v>
@@ -27582,7 +27579,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D136" s="14">
         <v>0</v>
@@ -27632,7 +27629,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D138" s="14">
         <v>0</v>
@@ -27657,7 +27654,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -27682,7 +27679,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D140" s="14">
         <v>0</v>
@@ -27757,7 +27754,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -27782,7 +27779,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -27807,7 +27804,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -27832,7 +27829,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D146" s="14">
         <v>0</v>
@@ -27857,7 +27854,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D147" s="14">
         <v>0</v>
@@ -27882,7 +27879,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D148" s="14">
         <v>0</v>
@@ -27907,7 +27904,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D149" s="14">
         <v>0</v>
@@ -27978,13 +27975,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D149">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28013,7 +28010,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -28038,7 +28035,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28047,7 +28044,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28084,7 +28081,7 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28109,7 +28106,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
@@ -28177,7 +28174,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="D15" s="14">
         <v>4740</v>
@@ -28227,7 +28224,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D17" s="14">
         <v>4300</v>
@@ -28252,7 +28249,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D18" s="14">
         <v>4200</v>
@@ -28277,7 +28274,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D19" s="14">
         <v>4020</v>
@@ -28302,7 +28299,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D20" s="14">
         <v>3980</v>
@@ -28327,7 +28324,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D21" s="14">
         <v>3780</v>
@@ -28352,7 +28349,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D22" s="14">
         <v>3710</v>
@@ -28377,7 +28374,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D23" s="14">
         <v>3650</v>
@@ -28427,7 +28424,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D25" s="14">
         <v>3600</v>
@@ -28452,7 +28449,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D26" s="14">
         <v>3460</v>
@@ -28502,7 +28499,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D28" s="14">
         <v>3360</v>
@@ -28602,7 +28599,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D32" s="14">
         <v>3120</v>
@@ -28627,7 +28624,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D33" s="14">
         <v>3060</v>
@@ -28802,7 +28799,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D40" s="14">
         <v>2720</v>
@@ -28852,7 +28849,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D42" s="14">
         <v>2660</v>
@@ -28902,7 +28899,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D44" s="14">
         <v>2640</v>
@@ -28952,7 +28949,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D46" s="14">
         <v>2600</v>
@@ -29002,7 +28999,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D48" s="14">
         <v>2550</v>
@@ -29052,7 +29049,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D50" s="14">
         <v>2540</v>
@@ -29127,7 +29124,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D53" s="14">
         <v>2460</v>
@@ -29152,7 +29149,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D54" s="14">
         <v>2460</v>
@@ -29202,7 +29199,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D56" s="14">
         <v>2420</v>
@@ -29277,7 +29274,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D59" s="14">
         <v>2400</v>
@@ -29377,7 +29374,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D63" s="14">
         <v>2340</v>
@@ -29402,7 +29399,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D64" s="14">
         <v>2330</v>
@@ -29427,7 +29424,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D65" s="14">
         <v>2300</v>
@@ -29527,7 +29524,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D69" s="14">
         <v>2190</v>
@@ -29552,7 +29549,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D70" s="14">
         <v>2150</v>
@@ -29577,7 +29574,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D71" s="14">
         <v>2140</v>
@@ -29702,7 +29699,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D76" s="14">
         <v>2130</v>
@@ -29727,7 +29724,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D77" s="14">
         <v>2120</v>
@@ -29777,7 +29774,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D79" s="14">
         <v>2100</v>
@@ -29902,7 +29899,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D84" s="14">
         <v>2050</v>
@@ -29927,7 +29924,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D85" s="14">
         <v>2040</v>
@@ -29977,7 +29974,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D87" s="14">
         <v>2040</v>
@@ -30027,7 +30024,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D89" s="14">
         <v>2000</v>
@@ -30077,7 +30074,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D91" s="14">
         <v>1960</v>
@@ -30127,7 +30124,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D93" s="14">
         <v>1920</v>
@@ -30152,7 +30149,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D94" s="14">
         <v>1920</v>
@@ -30177,7 +30174,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D95" s="14">
         <v>1900</v>
@@ -30202,7 +30199,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D96" s="14">
         <v>1880</v>
@@ -30302,7 +30299,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D100" s="14">
         <v>1660</v>
@@ -30327,7 +30324,7 @@
         <v>89</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D101" s="14">
         <v>1640</v>
@@ -30352,7 +30349,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D102" s="14">
         <v>1620</v>
@@ -30377,7 +30374,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D103" s="14">
         <v>1540</v>
@@ -30402,7 +30399,7 @@
         <v>92</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D104" s="14">
         <v>1520</v>
@@ -30427,7 +30424,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D105" s="14">
         <v>1460</v>
@@ -30452,7 +30449,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D106" s="14">
         <v>1460</v>
@@ -30477,7 +30474,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D107" s="14">
         <v>1400</v>
@@ -30602,7 +30599,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D112" s="14">
         <v>1220</v>
@@ -30677,7 +30674,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D115" s="14">
         <v>1030</v>
@@ -30702,7 +30699,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D116" s="14">
         <v>1000</v>
@@ -30727,7 +30724,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D117" s="14">
         <v>960</v>
@@ -30752,7 +30749,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D118" s="14">
         <v>910</v>
@@ -30827,7 +30824,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D121" s="14">
         <v>860</v>
@@ -30852,7 +30849,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D122" s="14">
         <v>840</v>
@@ -30877,7 +30874,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D123" s="14">
         <v>820</v>
@@ -30902,7 +30899,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D124" s="14">
         <v>770</v>
@@ -30927,7 +30924,7 @@
         <v>113</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D125" s="14">
         <v>720</v>
@@ -30977,7 +30974,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D127" s="14">
         <v>620</v>
@@ -31002,7 +30999,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D128" s="14">
         <v>600</v>
@@ -31052,7 +31049,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D130" s="14">
         <v>470</v>
@@ -31077,7 +31074,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D131" s="14">
         <v>360</v>
@@ -31102,7 +31099,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D132" s="14">
         <v>230</v>
@@ -31127,7 +31124,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D133" s="14">
         <v>220</v>
@@ -31152,7 +31149,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D134" s="14">
         <v>0</v>
@@ -31177,7 +31174,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D135" s="14">
         <v>0</v>
@@ -31202,7 +31199,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D136" s="14">
         <v>0</v>
@@ -31227,7 +31224,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D137" s="14">
         <v>0</v>
@@ -31252,7 +31249,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D138" s="14">
         <v>0</v>
@@ -31277,7 +31274,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -31352,7 +31349,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D142" s="14">
         <v>0</v>
@@ -31377,7 +31374,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -31402,7 +31399,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -31427,7 +31424,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -31452,7 +31449,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D146" s="14">
         <v>0</v>
@@ -31523,13 +31520,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D146">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>

--- a/alliance-mobilization.xlsx
+++ b/alliance-mobilization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\SynologyDrive\dgefers\Desktop\Rise of Kingdoms\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F94EDC-7C37-4118-9FD8-34F78BFA3188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9714B500-C1DB-4561-8C63-7544A4394671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{909B3E3F-35C1-45D2-894E-8B07AC82B732}"/>
+    <workbookView xWindow="12795" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="2" activeTab="8" xr2:uid="{909B3E3F-35C1-45D2-894E-8B07AC82B732}"/>
   </bookViews>
   <sheets>
     <sheet name="November 2025" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="July 2026" sheetId="6" r:id="rId6"/>
     <sheet name="August 2026" sheetId="5" r:id="rId7"/>
     <sheet name="September 2026" sheetId="8" r:id="rId8"/>
+    <sheet name="Name changes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'August 2026'!$12:$12</definedName>
@@ -223,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="384">
   <si>
     <t>Start</t>
   </si>
@@ -497,9 +498,6 @@
     <t>Kuba yes</t>
   </si>
   <si>
-    <t>Duweii</t>
-  </si>
-  <si>
     <t>Marbon3</t>
   </si>
   <si>
@@ -678,16 +676,7 @@
     <t>Angela D Pinili</t>
   </si>
   <si>
-    <t>mim sa chas (Farmer Gamma)</t>
-  </si>
-  <si>
-    <t>メOnlyFarmsメ (メLakotekメ)</t>
-  </si>
-  <si>
     <t>亗Andzia亗</t>
-  </si>
-  <si>
-    <t>ʚɞK BÉO (Viet Nam N1)</t>
   </si>
   <si>
     <t>Duweiii</t>
@@ -769,9 +758,6 @@
     <t>・Aziel・</t>
   </si>
   <si>
-    <t>AresF2 (RamONa F2)</t>
-  </si>
-  <si>
     <t>メOnlyFarmsメ</t>
   </si>
   <si>
@@ -793,18 +779,12 @@
     <t>PrZeMMeKᴾᴸ</t>
   </si>
   <si>
-    <t>Ares f (RamONa F1)</t>
-  </si>
-  <si>
     <t>Baby Boogy15</t>
   </si>
   <si>
     <t>Adrian3535</t>
   </si>
   <si>
-    <t>AresFf3 (RamONa F3)</t>
-  </si>
-  <si>
     <t>Sytheᴾᴴ</t>
   </si>
   <si>
@@ -826,9 +806,6 @@
     <t>missavfarmm</t>
   </si>
   <si>
-    <t>Aresツ(RamONa)</t>
-  </si>
-  <si>
     <t>SEMİHBZ14</t>
   </si>
   <si>
@@ -883,9 +860,6 @@
     <t>Monkey D・Sabo</t>
   </si>
   <si>
-    <t>Monkey D・Ace (Monkey D Bro)</t>
-  </si>
-  <si>
     <t>Level completed</t>
   </si>
   <si>
@@ -997,9 +971,6 @@
     <t>CihangirTR farm</t>
   </si>
   <si>
-    <t>FIRTINA</t>
-  </si>
-  <si>
     <t>AndziaINFmini7</t>
   </si>
   <si>
@@ -1127,9 +1098,6 @@
   </si>
   <si>
     <t>✗Adrian✗</t>
-  </si>
-  <si>
-    <t>PHSheeeshhh</t>
   </si>
   <si>
     <t>Andzia</t>
@@ -1262,9 +1230,6 @@
     <t>✞ Zoro Farm5 ✞</t>
   </si>
   <si>
-    <t>Mchorii</t>
-  </si>
-  <si>
     <t>MiniKaRa92</t>
   </si>
   <si>
@@ -1340,6 +1305,9 @@
     <t>WiedźmiN F10</t>
   </si>
   <si>
+    <t>ThaoLy F2P</t>
+  </si>
+  <si>
     <t>Tubylec Rss012</t>
   </si>
   <si>
@@ -1349,12 +1317,6 @@
     <t>4thLegionfarm</t>
   </si>
   <si>
-    <t>• Iceball • (✗ Ares ✗)</t>
-  </si>
-  <si>
-    <t>Beefball (arczi×D)</t>
-  </si>
-  <si>
     <t>F2bfarm</t>
   </si>
   <si>
@@ -1364,16 +1326,61 @@
     <t>Jaken Naga lulu</t>
   </si>
   <si>
-    <t>Dede Korkut 1 (CihangirTR)</t>
-  </si>
-  <si>
-    <t>✗ Ares ✗ (Aresツ)</t>
-  </si>
-  <si>
-    <t>ThaoLy F2P (Duweiii)</t>
-  </si>
-  <si>
-    <t>ANS FARMأ (ANS أ)</t>
+    <t>Current name</t>
+  </si>
+  <si>
+    <t>AresF2</t>
+  </si>
+  <si>
+    <t>RamONa F2</t>
+  </si>
+  <si>
+    <t>Ares f</t>
+  </si>
+  <si>
+    <t>RamONa F1</t>
+  </si>
+  <si>
+    <t>AresFf3</t>
+  </si>
+  <si>
+    <t>RamONa F3</t>
+  </si>
+  <si>
+    <t>RamONa</t>
+  </si>
+  <si>
+    <t>• Iceball •</t>
+  </si>
+  <si>
+    <t>Dede Korkut 1</t>
+  </si>
+  <si>
+    <t>Beefball</t>
+  </si>
+  <si>
+    <t>Alliance Mobilization: Name changes</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>FıRTINA</t>
+  </si>
+  <si>
+    <t>Former name 1</t>
+  </si>
+  <si>
+    <t>Former name 2</t>
+  </si>
+  <si>
+    <t>Former name 3</t>
+  </si>
+  <si>
+    <t>ᴾᴴSheeeshhh</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1559,176 +1566,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="151">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="157">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1968,6 +1814,288 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="1" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </diagonal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2388,17 +2516,96 @@
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2457,65 +2664,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2568,213 +2717,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="1" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <diagonal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </diagonal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2795,6 +2742,18 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2815,29 +2774,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2851,9 +2787,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3097,13 +3030,13 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Rise of Kingdoms" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Rise of Kingdoms" pivot="0" count="7" xr9:uid="{814AAECB-B283-4971-B156-CBB9C11E7CE1}">
-      <tableStyleElement type="wholeTable" dxfId="150"/>
-      <tableStyleElement type="headerRow" dxfId="149"/>
-      <tableStyleElement type="totalRow" dxfId="148"/>
-      <tableStyleElement type="firstColumn" dxfId="147"/>
-      <tableStyleElement type="lastColumn" dxfId="146"/>
-      <tableStyleElement type="firstRowStripe" dxfId="145"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="144"/>
+      <tableStyleElement type="wholeTable" dxfId="156"/>
+      <tableStyleElement type="headerRow" dxfId="155"/>
+      <tableStyleElement type="totalRow" dxfId="154"/>
+      <tableStyleElement type="firstColumn" dxfId="153"/>
+      <tableStyleElement type="lastColumn" dxfId="152"/>
+      <tableStyleElement type="firstRowStripe" dxfId="151"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="150"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3118,18 +3051,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}" name="AllianceMobilizationNovember2025" displayName="AllianceMobilizationNovember2025" ref="B12:G157" totalsRowCount="1" headerRowDxfId="134" dataDxfId="133" totalsRowDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}" name="AllianceMobilization202511" displayName="AllianceMobilization202511" ref="B12:G157" totalsRowCount="1" headerRowDxfId="140" dataDxfId="139" totalsRowDxfId="138">
   <autoFilter ref="B12:G156" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G156">
     <sortCondition ref="B12:B156"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E80EFDDD-CF56-40E0-84FA-EE7D9422EE02}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="131" totalsRowDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{3B6633FB-4D7C-4AE3-BAB1-89D7B440BAB2}" name="Governor" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{C9B4BB00-6F72-49A1-BC67-75C7DBA56D12}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="127" totalsRowDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{495DCF47-EE1A-43FF-BC77-24F1998BD592}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="5" xr3:uid="{5DA3BDD5-5ED1-4533-9FF2-9EA9C5A6505D}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="123" totalsRowDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{695CA109-E314-447D-8CC9-1DE4EBE1D106}" name="Points per_x000a_Quest compl." dataDxfId="121" totalsRowDxfId="120">
+    <tableColumn id="1" xr3:uid="{E80EFDDD-CF56-40E0-84FA-EE7D9422EE02}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="137" totalsRowDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{3B6633FB-4D7C-4AE3-BAB1-89D7B440BAB2}" name="Governor" dataDxfId="136" totalsRowDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{C9B4BB00-6F72-49A1-BC67-75C7DBA56D12}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="135" totalsRowDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{495DCF47-EE1A-43FF-BC77-24F1998BD592}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="134" totalsRowDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{5DA3BDD5-5ED1-4533-9FF2-9EA9C5A6505D}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="133" totalsRowDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{695CA109-E314-447D-8CC9-1DE4EBE1D106}" name="Points per_x000a_Quest compl." dataDxfId="132" totalsRowDxfId="42">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3138,18 +3071,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4C009E5-0657-4DF1-ADEB-1771FC5393CD}" name="AllianceMobilizationJanuary2026" displayName="AllianceMobilizationJanuary2026" ref="B12:G124" totalsRowCount="1" headerRowDxfId="119" dataDxfId="118" totalsRowDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4C009E5-0657-4DF1-ADEB-1771FC5393CD}" name="AllianceMobilization202601" displayName="AllianceMobilization202601" ref="B12:G124" totalsRowCount="1" headerRowDxfId="131" dataDxfId="130" totalsRowDxfId="129">
   <autoFilter ref="B12:G123" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G123">
     <sortCondition ref="B12:B123"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2E23F4F9-51DB-40ED-9226-3A3B014E70A6}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="116" totalsRowDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{8F7C649B-6D88-4F11-B796-32F33F442642}" name="Governor" dataDxfId="114" totalsRowDxfId="113"/>
-    <tableColumn id="3" xr3:uid="{2193B9C7-6D26-4A08-B094-729B3B441B48}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="111"/>
-    <tableColumn id="4" xr3:uid="{E4294EBA-4938-464A-8060-8F7F2F839DBE}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="110" totalsRowDxfId="109"/>
-    <tableColumn id="5" xr3:uid="{7FB251BF-169C-4924-83A6-069E02C7F5D2}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="107"/>
-    <tableColumn id="6" xr3:uid="{EBF17B55-1711-466D-8489-61F0248BF567}" name="Points per_x000a_Quest compl." dataDxfId="106" totalsRowDxfId="105">
+    <tableColumn id="1" xr3:uid="{2E23F4F9-51DB-40ED-9226-3A3B014E70A6}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="128" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{8F7C649B-6D88-4F11-B796-32F33F442642}" name="Governor" dataDxfId="127" totalsRowDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{2193B9C7-6D26-4A08-B094-729B3B441B48}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="126" totalsRowDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{E4294EBA-4938-464A-8060-8F7F2F839DBE}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{7FB251BF-169C-4924-83A6-069E02C7F5D2}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="124" totalsRowDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{EBF17B55-1711-466D-8489-61F0248BF567}" name="Points per_x000a_Quest compl." dataDxfId="123" totalsRowDxfId="36">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3158,18 +3091,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1D3B8002-176C-472A-94EF-BAA86E82E885}" name="AllianceMobilizationFebruary2026" displayName="AllianceMobilizationFebruary2026" ref="B12:G152" totalsRowCount="1" headerRowDxfId="104" dataDxfId="103" totalsRowDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1D3B8002-176C-472A-94EF-BAA86E82E885}" name="AllianceMobilization202602" displayName="AllianceMobilization202602" ref="B12:G152" totalsRowCount="1" headerRowDxfId="122" dataDxfId="121" totalsRowDxfId="120">
   <autoFilter ref="B12:G151" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G151">
     <sortCondition ref="B12:B151"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{B30EAC76-060F-4B49-90A4-959A62E0C548}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="101" totalsRowDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{06F94D66-C61F-4063-9650-9472D99D94DB}" name="Governor" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{6671FE25-D716-415E-9CC6-0747DC95F98D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="4" xr3:uid="{7F3CD8A8-5FB7-494E-8C4D-D884901E7CAD}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="94"/>
-    <tableColumn id="5" xr3:uid="{F7D5B1B8-846B-4525-BFE2-0E221E02DD5B}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{9BAA2795-21A9-4C74-AECE-58FD09C05E9B}" name="Points per_x000a_Quest compl." dataDxfId="91" totalsRowDxfId="90">
+    <tableColumn id="1" xr3:uid="{B30EAC76-060F-4B49-90A4-959A62E0C548}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="119" totalsRowDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{06F94D66-C61F-4063-9650-9472D99D94DB}" name="Governor" dataDxfId="118" totalsRowDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{6671FE25-D716-415E-9CC6-0747DC95F98D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="117" totalsRowDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{7F3CD8A8-5FB7-494E-8C4D-D884901E7CAD}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="116" totalsRowDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{F7D5B1B8-846B-4525-BFE2-0E221E02DD5B}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="115" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{9BAA2795-21A9-4C74-AECE-58FD09C05E9B}" name="Points per_x000a_Quest compl." dataDxfId="114" totalsRowDxfId="26">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3178,18 +3111,18 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E01E6D77-4F29-4434-85C0-E3884F5E01CB}" name="AllianceMobilizationMarch2026" displayName="AllianceMobilizationMarch2026" ref="B12:G145" totalsRowCount="1" headerRowDxfId="89" dataDxfId="88" totalsRowDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E01E6D77-4F29-4434-85C0-E3884F5E01CB}" name="AllianceMobilization202603" displayName="AllianceMobilization202603" ref="B12:G145" totalsRowCount="1" headerRowDxfId="113" dataDxfId="112" totalsRowDxfId="111">
   <autoFilter ref="B12:G144" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G144">
     <sortCondition ref="B12:B144"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8F1B437D-7DC7-4032-B373-39501AAC305A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="86" totalsRowDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{5748D8F1-4EB7-49DC-9F19-02F8544ADB80}" name="Governor" dataDxfId="85" totalsRowDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C16FF4F5-BE34-45C7-AC36-B2C513C2BD38}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{E81DD37D-FD17-4F66-B511-74896A7F0F2A}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{DC35B835-A19A-439D-893B-122792042439}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{1621615B-84A5-4D0B-B67B-14F5B8B6075A}" name="Points per_x000a_Quest compl." dataDxfId="81" totalsRowDxfId="24">
+    <tableColumn id="1" xr3:uid="{8F1B437D-7DC7-4032-B373-39501AAC305A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="110" totalsRowDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{5748D8F1-4EB7-49DC-9F19-02F8544ADB80}" name="Governor" dataDxfId="109" totalsRowDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{C16FF4F5-BE34-45C7-AC36-B2C513C2BD38}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{E81DD37D-FD17-4F66-B511-74896A7F0F2A}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="107" totalsRowDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{DC35B835-A19A-439D-893B-122792042439}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{1621615B-84A5-4D0B-B67B-14F5B8B6075A}" name="Points per_x000a_Quest compl." dataDxfId="105" totalsRowDxfId="72">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3198,18 +3131,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ED8FBDF9-FCC7-4C93-9B38-43FF67FDEB9E}" name="AllianceMobilizationMarch2026678" displayName="AllianceMobilizationMarch2026678" ref="B12:G132" totalsRowCount="1" headerRowDxfId="80" dataDxfId="79" totalsRowDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ED8FBDF9-FCC7-4C93-9B38-43FF67FDEB9E}" name="AllianceMobilization202606" displayName="AllianceMobilization202606" ref="B12:G132" totalsRowCount="1" headerRowDxfId="104" dataDxfId="103" totalsRowDxfId="102">
   <autoFilter ref="B12:G131" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G131">
     <sortCondition ref="B12:B131"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D8E9B715-1D59-4A60-9E31-0B5FEE63A12A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{67F290D2-0820-48FE-BB36-118CF7DC1854}" name="Governor" dataDxfId="76" totalsRowDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{3D97C902-1962-42BB-BF4A-70FBB84A275D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6F4B57EE-DD44-4C31-991C-14DA6FAEE2CC}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{674F52CC-ADC3-4CFF-AF18-0C3EE0B6A778}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="73" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{7956BB13-96CA-4BA6-AE82-6C3911FEF104}" name="Points per_x000a_Quest compl." dataDxfId="72" totalsRowDxfId="18">
+    <tableColumn id="1" xr3:uid="{D8E9B715-1D59-4A60-9E31-0B5FEE63A12A}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="101" totalsRowDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{67F290D2-0820-48FE-BB36-118CF7DC1854}" name="Governor" dataDxfId="100" totalsRowDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{3D97C902-1962-42BB-BF4A-70FBB84A275D}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{6F4B57EE-DD44-4C31-991C-14DA6FAEE2CC}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="98" totalsRowDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{674F52CC-ADC3-4CFF-AF18-0C3EE0B6A778}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{7956BB13-96CA-4BA6-AE82-6C3911FEF104}" name="Points per_x000a_Quest compl." dataDxfId="96" totalsRowDxfId="66">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3218,18 +3151,18 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C1877A37-602D-4929-A27F-182C37222BF1}" name="AllianceMobilizationMarch202667" displayName="AllianceMobilizationMarch202667" ref="B12:G153" totalsRowCount="1" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C1877A37-602D-4929-A27F-182C37222BF1}" name="AllianceMobilization202607" displayName="AllianceMobilization202607" ref="B12:G153" totalsRowCount="1" headerRowDxfId="95" dataDxfId="94" totalsRowDxfId="93">
   <autoFilter ref="B12:G152" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G152">
     <sortCondition ref="B12:B152"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{024374DF-58D9-4D7E-A2F8-E94E3FDE62D4}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="68" totalsRowDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{63C21810-283C-483A-9B6F-5290EE4535DE}" name="Governor" dataDxfId="67" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{32C633D8-BA68-4EF3-BDCF-75E0D0078BCA}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{D1311703-382D-425F-A173-91EEC303E293}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{0A4AC45F-A60F-4A6F-9A75-E0BCC22CB6F0}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{78CAC145-EDB3-425A-A337-3F1234C5B602}" name="Points per_x000a_Quest compl." dataDxfId="63" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{024374DF-58D9-4D7E-A2F8-E94E3FDE62D4}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="92" totalsRowDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{63C21810-283C-483A-9B6F-5290EE4535DE}" name="Governor" dataDxfId="91" totalsRowDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{32C633D8-BA68-4EF3-BDCF-75E0D0078BCA}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{D1311703-382D-425F-A173-91EEC303E293}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{0A4AC45F-A60F-4A6F-9A75-E0BCC22CB6F0}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="88" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{78CAC145-EDB3-425A-A337-3F1234C5B602}" name="Points per_x000a_Quest compl." dataDxfId="87" totalsRowDxfId="48">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3238,18 +3171,18 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0E6F41ED-D120-45F9-8558-56F61F3BD8B0}" name="AllianceMobilizationMarch20266" displayName="AllianceMobilizationMarch20266" ref="B12:G150" totalsRowCount="1" headerRowDxfId="62" dataDxfId="61" totalsRowDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0E6F41ED-D120-45F9-8558-56F61F3BD8B0}" name="AllianceMobilization202608" displayName="AllianceMobilization202608" ref="B12:G150" totalsRowCount="1" headerRowDxfId="86" dataDxfId="85" totalsRowDxfId="84">
   <autoFilter ref="B12:G149" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G149">
     <sortCondition ref="B12:B149"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{50D3F7F9-6587-4E14-9172-32543B79C5F3}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="59" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{4BB8DE34-B1C7-4669-94D2-DFACA05ED05A}" name="Governor" dataDxfId="58" totalsRowDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{4E94BDE2-12D0-4603-9BB3-91BDDE3B74F4}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{1390E1DB-6F54-4A1B-8886-BA8A8C22BB6D}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{0F97E3EF-FD9E-46CF-9FE4-6549B5704E98}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{9863C91B-4251-4CB7-BB1D-4FE464EF7779}" name="Points per_x000a_Quest compl." dataDxfId="54" totalsRowDxfId="12">
+    <tableColumn id="1" xr3:uid="{50D3F7F9-6587-4E14-9172-32543B79C5F3}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="83" totalsRowDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{4BB8DE34-B1C7-4669-94D2-DFACA05ED05A}" name="Governor" dataDxfId="82" totalsRowDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{4E94BDE2-12D0-4603-9BB3-91BDDE3B74F4}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{1390E1DB-6F54-4A1B-8886-BA8A8C22BB6D}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{0F97E3EF-FD9E-46CF-9FE4-6549B5704E98}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{9863C91B-4251-4CB7-BB1D-4FE464EF7779}" name="Points per_x000a_Quest compl." dataDxfId="78" totalsRowDxfId="60">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3258,20 +3191,36 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D7D434E4-0568-420F-AA53-F95B11309638}" name="AllianceMobilizationMarch202669" displayName="AllianceMobilizationMarch202669" ref="B12:G147" totalsRowCount="1" headerRowDxfId="143" dataDxfId="142" totalsRowDxfId="141">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D7D434E4-0568-420F-AA53-F95B11309638}" name="AllianceMobilization202609" displayName="AllianceMobilization202609" ref="B12:G147" totalsRowCount="1" headerRowDxfId="149" dataDxfId="148" totalsRowDxfId="147">
   <autoFilter ref="B12:G146" xr:uid="{9F2171E4-5234-4B65-BCA7-CC3D483EA3FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G146">
     <sortCondition ref="B12:B146"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0BD6F31C-88ED-4F5D-B312-0E80EA472799}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="140" totalsRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{5476817D-6BB2-4219-BAAC-93030D81F834}" name="Governor" dataDxfId="139" totalsRowDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2F5807B0-B0CD-4270-8190-6228514D5EB9}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="138" totalsRowDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{66A94722-A980-4C21-AD3A-4DE5F6442EE7}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="137" totalsRowDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{FA7AC61E-5D38-40A4-AFEF-2DF13BCBF7BB}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="136" totalsRowDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{8CB484E1-EBED-4CF2-A72C-F49F44A142FD}" name="Points per_x000a_Quest compl." dataDxfId="135" totalsRowDxfId="6">
+    <tableColumn id="1" xr3:uid="{0BD6F31C-88ED-4F5D-B312-0E80EA472799}" name="Event_x000a_Rank" totalsRowLabel="Total" dataDxfId="146" totalsRowDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{5476817D-6BB2-4219-BAAC-93030D81F834}" name="Governor" dataDxfId="145" totalsRowDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{2F5807B0-B0CD-4270-8190-6228514D5EB9}" name="Points_x000a_reached" totalsRowFunction="sum" dataDxfId="144" totalsRowDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{66A94722-A980-4C21-AD3A-4DE5F6442EE7}" name="Quests_x000a_started" totalsRowFunction="sum" dataDxfId="143" totalsRowDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{FA7AC61E-5D38-40A4-AFEF-2DF13BCBF7BB}" name="Quests_x000a_completed" totalsRowFunction="sum" dataDxfId="142" totalsRowDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{8CB484E1-EBED-4CF2-A72C-F49F44A142FD}" name="Points per_x000a_Quest compl." dataDxfId="141" totalsRowDxfId="54">
       <calculatedColumnFormula>IFERROR(D13/F13,0)</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Rise of Kingdoms" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55DBD4E3-26E5-4E45-8E96-77D6F8230EB9}" name="AllianceMobilizationNameChanges" displayName="AllianceMobilizationNameChanges" ref="B7:E21" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="B7:E21" xr:uid="{55DBD4E3-26E5-4E45-8E96-77D6F8230EB9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:E21">
+    <sortCondition ref="B7:B21"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{CC994515-F24A-45D9-9B22-FB8EC5CA0084}" name="Current name" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{F9331BE2-A760-46EF-952B-849942869351}" name="Former name 1" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{9B887ADD-34DD-4696-9E85-79E76979C7C0}" name="Former name 2" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{AD294B23-055C-419A-AD07-93B9DAABB87A}" name="Former name 3" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="Rise of Kingdoms" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3605,7 +3554,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3617,7 +3566,7 @@
     </row>
     <row r="3" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -3663,7 +3612,7 @@
     <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -3680,7 +3629,7 @@
     </row>
     <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -3691,7 +3640,7 @@
     <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -3700,13 +3649,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -3893,7 +3842,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D20" s="15">
         <v>3310</v>
@@ -3918,7 +3867,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D21" s="15">
         <v>3300</v>
@@ -3968,7 +3917,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" s="15">
         <v>3220</v>
@@ -4018,7 +3967,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" s="15">
         <v>3120</v>
@@ -4043,7 +3992,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="15">
         <v>2960</v>
@@ -4068,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D27" s="15">
         <v>2920</v>
@@ -4093,7 +4042,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D28" s="15">
         <v>2910</v>
@@ -4118,7 +4067,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D29" s="15">
         <v>2880</v>
@@ -4168,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="15">
         <v>2860</v>
@@ -4218,7 +4167,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D33" s="15">
         <v>2850</v>
@@ -4243,7 +4192,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" s="15">
         <v>2820</v>
@@ -4443,7 +4392,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D42" s="15">
         <v>2660</v>
@@ -4493,7 +4442,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D44" s="15">
         <v>2580</v>
@@ -4543,7 +4492,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" s="15">
         <v>2580</v>
@@ -4668,7 +4617,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D51" s="15">
         <v>2530</v>
@@ -4768,7 +4717,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D55" s="15">
         <v>2440</v>
@@ -4868,7 +4817,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D59" s="15">
         <v>2400</v>
@@ -4968,7 +4917,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D63" s="15">
         <v>2210</v>
@@ -4993,7 +4942,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D64" s="15">
         <v>2200</v>
@@ -5018,7 +4967,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D65" s="15">
         <v>2190</v>
@@ -5043,7 +4992,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D66" s="15">
         <v>2180</v>
@@ -5068,7 +5017,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D67" s="15">
         <v>2180</v>
@@ -5168,7 +5117,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D71" s="15">
         <v>2100</v>
@@ -5193,7 +5142,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D72" s="15">
         <v>2090</v>
@@ -5218,7 +5167,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D73" s="15">
         <v>2080</v>
@@ -5243,7 +5192,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D74" s="15">
         <v>2080</v>
@@ -5268,7 +5217,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D75" s="15">
         <v>2060</v>
@@ -5343,7 +5292,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="15">
         <v>2030</v>
@@ -5368,7 +5317,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D79" s="15">
         <v>2010</v>
@@ -5543,7 +5492,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D86" s="15">
         <v>1780</v>
@@ -5593,7 +5542,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D88" s="15">
         <v>1730</v>
@@ -5643,7 +5592,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D90" s="15">
         <v>1700</v>
@@ -5718,7 +5667,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D93" s="15">
         <v>1630</v>
@@ -5743,7 +5692,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D94" s="15">
         <v>1630</v>
@@ -5818,7 +5767,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D97" s="15">
         <v>1600</v>
@@ -5943,7 +5892,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D102" s="15">
         <v>1570</v>
@@ -5968,7 +5917,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D103" s="15">
         <v>1560</v>
@@ -6143,7 +6092,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D110" s="15">
         <v>1380</v>
@@ -6243,7 +6192,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D114" s="15">
         <v>1350</v>
@@ -6468,7 +6417,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D123" s="15">
         <v>1270</v>
@@ -6543,7 +6492,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D126" s="15">
         <v>1250</v>
@@ -6568,7 +6517,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="D127" s="15">
         <v>1240</v>
@@ -6593,7 +6542,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D128" s="15">
         <v>1240</v>
@@ -6618,7 +6567,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D129" s="15">
         <v>1240</v>
@@ -6643,7 +6592,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D130" s="15">
         <v>1230</v>
@@ -6668,7 +6617,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="15">
         <v>1230</v>
@@ -6693,7 +6642,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D132" s="15">
         <v>1220</v>
@@ -6718,7 +6667,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D133" s="15">
         <v>1220</v>
@@ -6743,7 +6692,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D134" s="15">
         <v>1210</v>
@@ -6768,7 +6717,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D135" s="15">
         <v>1210</v>
@@ -6793,7 +6742,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D136" s="15">
         <v>1210</v>
@@ -6818,7 +6767,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D137" s="15">
         <v>1200</v>
@@ -6843,7 +6792,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D138" s="15">
         <v>1200</v>
@@ -6868,7 +6817,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D139" s="15">
         <v>1200</v>
@@ -6893,7 +6842,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D140" s="15">
         <v>1160</v>
@@ -6918,7 +6867,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D141" s="15">
         <v>1100</v>
@@ -6943,7 +6892,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D142" s="15">
         <v>910</v>
@@ -6968,7 +6917,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D143" s="15">
         <v>860</v>
@@ -6993,7 +6942,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D144" s="15">
         <v>770</v>
@@ -7018,7 +6967,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D145" s="15">
         <v>760</v>
@@ -7043,7 +6992,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D146" s="15">
         <v>710</v>
@@ -7068,7 +7017,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D147" s="15">
         <v>470</v>
@@ -7093,7 +7042,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D148" s="15">
         <v>360</v>
@@ -7118,7 +7067,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D149" s="15">
         <v>360</v>
@@ -7143,7 +7092,7 @@
         <v>138</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D150" s="15">
         <v>300</v>
@@ -7218,7 +7167,7 @@
         <v>141</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D153" s="15">
         <v>0</v>
@@ -7311,21 +7260,21 @@
     </row>
     <row r="157" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B157" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C157" s="12"/>
       <c r="D157" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationNovember2025[Points
+        <f>SUBTOTAL(109,AllianceMobilization202511[Points
 reached])</f>
         <v>279760</v>
       </c>
       <c r="E157" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationNovember2025[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202511[Quests
 started])</f>
         <v>1631</v>
       </c>
       <c r="F157" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationNovember2025[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202511[Quests
 completed])</f>
         <v>1632</v>
       </c>
@@ -7333,7 +7282,7 @@
     </row>
     <row r="158" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B158" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="8">
@@ -7364,13 +7313,13 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D156">
-    <cfRule type="cellIs" dxfId="53" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7395,7 +7344,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -7407,7 +7356,7 @@
     </row>
     <row r="3" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -7420,7 +7369,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7429,7 +7378,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7447,13 +7396,13 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -7470,7 +7419,7 @@
     </row>
     <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -7481,7 +7430,7 @@
     <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -7490,13 +7439,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7533,7 +7482,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" s="15">
         <v>8280</v>
@@ -7633,7 +7582,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D18" s="15">
         <v>4700</v>
@@ -7658,7 +7607,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D19" s="15">
         <v>4700</v>
@@ -7708,7 +7657,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="15">
         <v>4030</v>
@@ -7733,7 +7682,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="D22" s="15">
         <v>3990</v>
@@ -7783,7 +7732,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D24" s="15">
         <v>3400</v>
@@ -7858,7 +7807,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D27" s="15">
         <v>3200</v>
@@ -7883,7 +7832,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="15">
         <v>3170</v>
@@ -8033,7 +7982,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D34" s="15">
         <v>2980</v>
@@ -8133,7 +8082,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D38" s="15">
         <v>2680</v>
@@ -8208,7 +8157,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D41" s="15">
         <v>2640</v>
@@ -8258,7 +8207,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="D43" s="15">
         <v>2600</v>
@@ -8358,7 +8307,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D47" s="15">
         <v>2560</v>
@@ -8383,7 +8332,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D48" s="15">
         <v>2540</v>
@@ -8408,7 +8357,7 @@
         <v>37</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D49" s="15">
         <v>2530</v>
@@ -8458,7 +8407,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D51" s="15">
         <v>2500</v>
@@ -8483,7 +8432,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D52" s="15">
         <v>2480</v>
@@ -8508,7 +8457,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D53" s="15">
         <v>2460</v>
@@ -8558,7 +8507,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D55" s="15">
         <v>2440</v>
@@ -8608,7 +8557,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D57" s="15">
         <v>2420</v>
@@ -8658,7 +8607,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D59" s="15">
         <v>2350</v>
@@ -8708,7 +8657,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D61" s="15">
         <v>2290</v>
@@ -8758,7 +8707,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D63" s="15">
         <v>2280</v>
@@ -8833,7 +8782,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D66" s="15">
         <v>2250</v>
@@ -8858,7 +8807,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D67" s="15">
         <v>2250</v>
@@ -8933,7 +8882,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D70" s="15">
         <v>2160</v>
@@ -8958,7 +8907,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D71" s="15">
         <v>2160</v>
@@ -8983,7 +8932,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="15">
         <v>2160</v>
@@ -9008,7 +8957,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D73" s="15">
         <v>2060</v>
@@ -9058,7 +9007,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D75" s="15">
         <v>2040</v>
@@ -9083,7 +9032,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D76" s="15">
         <v>2020</v>
@@ -9108,7 +9057,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D77" s="15">
         <v>2000</v>
@@ -9133,7 +9082,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D78" s="15">
         <v>1980</v>
@@ -9183,7 +9132,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D80" s="15">
         <v>1920</v>
@@ -9208,7 +9157,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D81" s="15">
         <v>1920</v>
@@ -9233,7 +9182,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D82" s="15">
         <v>1920</v>
@@ -9308,7 +9257,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D85" s="15">
         <v>1880</v>
@@ -9333,7 +9282,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="15">
         <v>1870</v>
@@ -9383,7 +9332,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D88" s="15">
         <v>1800</v>
@@ -9408,7 +9357,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D89" s="15">
         <v>1780</v>
@@ -9458,7 +9407,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D91" s="15">
         <v>1740</v>
@@ -9483,7 +9432,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D92" s="15">
         <v>1720</v>
@@ -9508,7 +9457,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D93" s="15">
         <v>1700</v>
@@ -9533,7 +9482,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D94" s="15">
         <v>1700</v>
@@ -9583,7 +9532,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D96" s="15">
         <v>1670</v>
@@ -9608,7 +9557,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D97" s="15">
         <v>1670</v>
@@ -9658,7 +9607,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D99" s="15">
         <v>1660</v>
@@ -9683,7 +9632,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D100" s="15">
         <v>1640</v>
@@ -9708,7 +9657,7 @@
         <v>89</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D101" s="15">
         <v>1640</v>
@@ -9733,7 +9682,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D102" s="15">
         <v>1640</v>
@@ -9758,7 +9707,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D103" s="15">
         <v>1600</v>
@@ -9808,7 +9757,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D105" s="15">
         <v>1570</v>
@@ -9833,7 +9782,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D106" s="15">
         <v>1560</v>
@@ -9883,7 +9832,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D108" s="15">
         <v>1560</v>
@@ -9933,7 +9882,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D110" s="15">
         <v>1530</v>
@@ -10008,7 +9957,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D113" s="15">
         <v>1500</v>
@@ -10033,7 +9982,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D114" s="15">
         <v>1500</v>
@@ -10058,7 +10007,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D115" s="15">
         <v>1480</v>
@@ -10083,7 +10032,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="15">
         <v>1240</v>
@@ -10108,7 +10057,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="D117" s="15">
         <v>1170</v>
@@ -10133,7 +10082,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D118" s="15">
         <v>1150</v>
@@ -10158,7 +10107,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D119" s="15">
         <v>960</v>
@@ -10183,7 +10132,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D120" s="15">
         <v>360</v>
@@ -10258,7 +10207,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D123" s="15">
         <v>0</v>
@@ -10276,21 +10225,21 @@
     </row>
     <row r="124" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B124" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C124" s="12"/>
       <c r="D124" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationJanuary2026[Points
+        <f>SUBTOTAL(109,AllianceMobilization202601[Points
 reached])</f>
         <v>268580</v>
       </c>
       <c r="E124" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationJanuary2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202601[Quests
 started])</f>
         <v>1558</v>
       </c>
       <c r="F124" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationJanuary2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202601[Quests
 completed])</f>
         <v>1569</v>
       </c>
@@ -10298,7 +10247,7 @@
     </row>
     <row r="125" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B125" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="6">
@@ -10329,13 +10278,13 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D123">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10363,7 +10312,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -10375,7 +10324,7 @@
     </row>
     <row r="3" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -10388,7 +10337,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -10397,7 +10346,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -10415,13 +10364,13 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -10433,12 +10382,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -10449,7 +10398,7 @@
     <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -10458,13 +10407,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -10501,7 +10450,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D14" s="15">
         <v>5940</v>
@@ -10551,7 +10500,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D16" s="15">
         <v>5480</v>
@@ -10601,7 +10550,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D18" s="15">
         <v>3740</v>
@@ -10626,7 +10575,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D19" s="15">
         <v>3720</v>
@@ -10651,7 +10600,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D20" s="15">
         <v>3700</v>
@@ -10676,7 +10625,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D21" s="15">
         <v>3700</v>
@@ -10726,7 +10675,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D23" s="15">
         <v>3440</v>
@@ -10751,7 +10700,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D24" s="15">
         <v>3180</v>
@@ -10776,7 +10725,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D25" s="15">
         <v>3160</v>
@@ -10801,7 +10750,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D26" s="15">
         <v>3050</v>
@@ -10826,7 +10775,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D27" s="15">
         <v>3010</v>
@@ -10851,7 +10800,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" s="15">
         <v>2890</v>
@@ -10876,7 +10825,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D29" s="15">
         <v>2820</v>
@@ -10901,7 +10850,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D30" s="15">
         <v>2800</v>
@@ -10926,7 +10875,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D31" s="15">
         <v>2800</v>
@@ -10951,7 +10900,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D32" s="15">
         <v>2780</v>
@@ -11051,7 +11000,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D36" s="15">
         <v>2580</v>
@@ -11076,7 +11025,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D37" s="15">
         <v>2580</v>
@@ -11101,7 +11050,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D38" s="15">
         <v>2560</v>
@@ -11126,7 +11075,7 @@
         <v>27</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D39" s="15">
         <v>2520</v>
@@ -11151,7 +11100,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D40" s="15">
         <v>2500</v>
@@ -11176,7 +11125,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D41" s="15">
         <v>2460</v>
@@ -11201,7 +11150,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D42" s="15">
         <v>2460</v>
@@ -11226,7 +11175,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="15">
         <v>2420</v>
@@ -11401,7 +11350,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D50" s="15">
         <v>2370</v>
@@ -11426,7 +11375,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D51" s="15">
         <v>2350</v>
@@ -11501,7 +11450,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D54" s="15">
         <v>2300</v>
@@ -11526,7 +11475,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>180</v>
+        <v>366</v>
       </c>
       <c r="D55" s="15">
         <v>2300</v>
@@ -11551,7 +11500,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D56" s="15">
         <v>2300</v>
@@ -11576,7 +11525,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D57" s="15">
         <v>2280</v>
@@ -11626,7 +11575,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59" s="15">
         <v>2270</v>
@@ -11651,7 +11600,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D60" s="15">
         <v>2260</v>
@@ -11676,7 +11625,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D61" s="15">
         <v>2240</v>
@@ -11701,7 +11650,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D62" s="15">
         <v>2240</v>
@@ -11726,7 +11675,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D63" s="15">
         <v>2230</v>
@@ -11751,7 +11700,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D64" s="15">
         <v>2230</v>
@@ -11776,7 +11725,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="15">
         <v>2220</v>
@@ -11801,7 +11750,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D66" s="15">
         <v>2220</v>
@@ -11826,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D67" s="15">
         <v>2210</v>
@@ -11976,7 +11925,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D73" s="15">
         <v>2160</v>
@@ -12026,7 +11975,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D75" s="15">
         <v>2140</v>
@@ -12076,7 +12025,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D77" s="15">
         <v>2140</v>
@@ -12126,7 +12075,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D79" s="15">
         <v>2130</v>
@@ -12176,7 +12125,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D81" s="15">
         <v>2120</v>
@@ -12201,7 +12150,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D82" s="15">
         <v>2120</v>
@@ -12226,7 +12175,7 @@
         <v>71</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D83" s="15">
         <v>2110</v>
@@ -12251,7 +12200,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D84" s="15">
         <v>2110</v>
@@ -12301,7 +12250,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D86" s="15">
         <v>2100</v>
@@ -12351,7 +12300,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D88" s="15">
         <v>2080</v>
@@ -12401,7 +12350,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>188</v>
+        <v>368</v>
       </c>
       <c r="D90" s="15">
         <v>2070</v>
@@ -12426,7 +12375,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D91" s="15">
         <v>2070</v>
@@ -12451,7 +12400,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D92" s="15">
         <v>2060</v>
@@ -12601,7 +12550,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D98" s="15">
         <v>2040</v>
@@ -12626,7 +12575,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D99" s="15">
         <v>2040</v>
@@ -12651,7 +12600,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="D100" s="15">
         <v>2040</v>
@@ -12751,7 +12700,7 @@
         <v>92</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D104" s="15">
         <v>2040</v>
@@ -12776,7 +12725,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D105" s="15">
         <v>2030</v>
@@ -12826,7 +12775,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D107" s="15">
         <v>2030</v>
@@ -12851,7 +12800,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D108" s="15">
         <v>2030</v>
@@ -12901,7 +12850,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D110" s="15">
         <v>2020</v>
@@ -12926,7 +12875,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D111" s="15">
         <v>2020</v>
@@ -12951,7 +12900,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D112" s="15">
         <v>2020</v>
@@ -13001,7 +12950,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D114" s="15">
         <v>2020</v>
@@ -13026,7 +12975,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D115" s="15">
         <v>2020</v>
@@ -13051,7 +13000,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D116" s="15">
         <v>2020</v>
@@ -13076,7 +13025,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D117" s="15">
         <v>2010</v>
@@ -13126,7 +13075,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D119" s="15">
         <v>2010</v>
@@ -13151,7 +13100,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D120" s="15">
         <v>2010</v>
@@ -13176,7 +13125,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="D121" s="15">
         <v>2010</v>
@@ -13201,7 +13150,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D122" s="15">
         <v>2010</v>
@@ -13226,7 +13175,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D123" s="15">
         <v>2010</v>
@@ -13251,7 +13200,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D124" s="15">
         <v>2010</v>
@@ -13276,7 +13225,7 @@
         <v>113</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D125" s="15">
         <v>2000</v>
@@ -13326,7 +13275,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D127" s="15">
         <v>2000</v>
@@ -13376,7 +13325,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D129" s="15">
         <v>2000</v>
@@ -13401,7 +13350,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D130" s="15">
         <v>2000</v>
@@ -13426,7 +13375,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D131" s="15">
         <v>2000</v>
@@ -13451,7 +13400,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D132" s="15">
         <v>2000</v>
@@ -13476,7 +13425,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D133" s="15">
         <v>1870</v>
@@ -13501,7 +13450,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D134" s="15">
         <v>1740</v>
@@ -13551,7 +13500,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D136" s="15">
         <v>1620</v>
@@ -13601,7 +13550,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D138" s="15">
         <v>1600</v>
@@ -13626,7 +13575,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D139" s="15">
         <v>1260</v>
@@ -13676,7 +13625,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D141" s="15">
         <v>1240</v>
@@ -13701,7 +13650,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D142" s="15">
         <v>1240</v>
@@ -13726,7 +13675,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D143" s="15">
         <v>1210</v>
@@ -13751,7 +13700,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D144" s="15">
         <v>1000</v>
@@ -13776,7 +13725,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D145" s="15">
         <v>920</v>
@@ -13801,7 +13750,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D146" s="15">
         <v>800</v>
@@ -13826,7 +13775,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D147" s="15">
         <v>800</v>
@@ -13851,7 +13800,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D148" s="15">
         <v>90</v>
@@ -13876,7 +13825,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D149" s="15">
         <v>0</v>
@@ -13900,7 +13849,7 @@
         <v>138</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D150" s="15">
         <v>0</v>
@@ -13925,7 +13874,7 @@
         <v>139</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D151" s="15">
         <v>0</v>
@@ -13943,21 +13892,21 @@
     </row>
     <row r="152" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B152" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C152" s="12"/>
       <c r="D152" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationFebruary2026[Points
+        <f>SUBTOTAL(109,AllianceMobilization202602[Points
 reached])</f>
         <v>313350</v>
       </c>
       <c r="E152" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationFebruary2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202602[Quests
 started])</f>
         <v>1830</v>
       </c>
       <c r="F152" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationFebruary2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202602[Quests
 completed])</f>
         <v>1835</v>
       </c>
@@ -13965,7 +13914,7 @@
     </row>
     <row r="153" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B153" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C153" s="5"/>
       <c r="D153" s="6">
@@ -13996,13 +13945,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D151">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14030,7 +13979,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -14042,7 +13991,7 @@
     </row>
     <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -14055,7 +14004,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -14064,7 +14013,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -14089,7 +14038,7 @@
     <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -14101,12 +14050,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -14117,7 +14066,7 @@
     <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -14126,13 +14075,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -14144,7 +14093,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D13" s="15">
         <v>7020</v>
@@ -14169,7 +14118,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D14" s="15">
         <v>4860</v>
@@ -14194,7 +14143,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15">
         <v>4700</v>
@@ -14269,7 +14218,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D18" s="15">
         <v>4140</v>
@@ -14294,7 +14243,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D19" s="15">
         <v>4100</v>
@@ -14369,7 +14318,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D22" s="15">
         <v>3250</v>
@@ -14394,7 +14343,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D23" s="15">
         <v>3240</v>
@@ -14419,7 +14368,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D24" s="15">
         <v>3130</v>
@@ -14444,7 +14393,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D25" s="15">
         <v>3030</v>
@@ -14469,7 +14418,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="15">
         <v>2940</v>
@@ -14494,7 +14443,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D27" s="15">
         <v>2900</v>
@@ -14519,7 +14468,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D28" s="15">
         <v>2890</v>
@@ -14544,7 +14493,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D29" s="15">
         <v>2860</v>
@@ -14569,7 +14518,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D30" s="15">
         <v>2770</v>
@@ -14594,7 +14543,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D31" s="15">
         <v>2640</v>
@@ -14619,7 +14568,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D32" s="15">
         <v>2630</v>
@@ -14669,7 +14618,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D34" s="15">
         <v>2580</v>
@@ -14694,7 +14643,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D35" s="15">
         <v>2580</v>
@@ -14719,7 +14668,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="15">
         <v>2560</v>
@@ -14744,7 +14693,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D37" s="15">
         <v>2550</v>
@@ -14819,7 +14768,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D40" s="15">
         <v>2520</v>
@@ -14844,7 +14793,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" s="15">
         <v>2510</v>
@@ -14869,7 +14818,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D42" s="15">
         <v>2500</v>
@@ -14919,7 +14868,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D44" s="15">
         <v>2460</v>
@@ -14944,7 +14893,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D45" s="15">
         <v>2440</v>
@@ -14969,7 +14918,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D46" s="15">
         <v>2440</v>
@@ -14994,7 +14943,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D47" s="15">
         <v>2420</v>
@@ -15044,7 +14993,7 @@
         <v>37</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D49" s="15">
         <v>2390</v>
@@ -15069,7 +15018,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D50" s="15">
         <v>2380</v>
@@ -15094,7 +15043,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D51" s="15">
         <v>2360</v>
@@ -15119,7 +15068,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D52" s="15">
         <v>2350</v>
@@ -15144,7 +15093,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D53" s="15">
         <v>2280</v>
@@ -15244,7 +15193,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D57" s="15">
         <v>2250</v>
@@ -15269,7 +15218,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D58" s="15">
         <v>2250</v>
@@ -15294,7 +15243,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D59" s="15">
         <v>2230</v>
@@ -15369,7 +15318,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D62" s="15">
         <v>2200</v>
@@ -15494,7 +15443,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D67" s="15">
         <v>2170</v>
@@ -15519,7 +15468,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D68" s="15">
         <v>2160</v>
@@ -15544,7 +15493,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D69" s="15">
         <v>2150</v>
@@ -15594,7 +15543,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D71" s="15">
         <v>2140</v>
@@ -15619,7 +15568,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D72" s="15">
         <v>2130</v>
@@ -15644,7 +15593,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D73" s="15">
         <v>2120</v>
@@ -15694,7 +15643,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D75" s="15">
         <v>2070</v>
@@ -15719,7 +15668,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D76" s="15">
         <v>2060</v>
@@ -15744,7 +15693,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D77" s="15">
         <v>2060</v>
@@ -15794,7 +15743,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D79" s="15">
         <v>2050</v>
@@ -15819,7 +15768,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D80" s="15">
         <v>2040</v>
@@ -15844,7 +15793,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D81" s="15">
         <v>2020</v>
@@ -15869,7 +15818,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D82" s="15">
         <v>2020</v>
@@ -15894,7 +15843,7 @@
         <v>71</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D83" s="15">
         <v>2020</v>
@@ -15919,7 +15868,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D84" s="15">
         <v>2020</v>
@@ -15969,7 +15918,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D86" s="15">
         <v>2010</v>
@@ -15994,7 +15943,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D87" s="15">
         <v>2000</v>
@@ -16019,7 +15968,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D88" s="15">
         <v>2000</v>
@@ -16069,7 +16018,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D90" s="15">
         <v>1980</v>
@@ -16144,7 +16093,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D93" s="15">
         <v>1960</v>
@@ -16169,7 +16118,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D94" s="15">
         <v>1960</v>
@@ -16194,7 +16143,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D95" s="15">
         <v>1920</v>
@@ -16219,7 +16168,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D96" s="15">
         <v>1920</v>
@@ -16244,7 +16193,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D97" s="15">
         <v>1920</v>
@@ -16269,7 +16218,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D98" s="15">
         <v>1910</v>
@@ -16294,7 +16243,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D99" s="15">
         <v>1900</v>
@@ -16319,7 +16268,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D100" s="15">
         <v>1900</v>
@@ -16369,7 +16318,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" s="15">
         <v>1890</v>
@@ -16444,7 +16393,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D105" s="15">
         <v>1880</v>
@@ -16469,7 +16418,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D106" s="15">
         <v>1870</v>
@@ -16494,7 +16443,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D107" s="15">
         <v>1860</v>
@@ -16544,7 +16493,7 @@
         <v>97</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D109" s="15">
         <v>1840</v>
@@ -16619,7 +16568,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D112" s="15">
         <v>1830</v>
@@ -16669,7 +16618,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D114" s="15">
         <v>1820</v>
@@ -16694,7 +16643,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D115" s="15">
         <v>1820</v>
@@ -16719,7 +16668,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D116" s="15">
         <v>1820</v>
@@ -16744,7 +16693,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D117" s="15">
         <v>1820</v>
@@ -16769,7 +16718,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D118" s="15">
         <v>1810</v>
@@ -16794,7 +16743,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D119" s="15">
         <v>1810</v>
@@ -16819,7 +16768,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D120" s="15">
         <v>1800</v>
@@ -16844,7 +16793,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D121" s="15">
         <v>1800</v>
@@ -16869,7 +16818,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D122" s="15">
         <v>1800</v>
@@ -16919,7 +16868,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D124" s="15">
         <v>1800</v>
@@ -16969,7 +16918,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D126" s="15">
         <v>1460</v>
@@ -16994,7 +16943,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D127" s="15">
         <v>1460</v>
@@ -17019,7 +16968,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D128" s="15">
         <v>1420</v>
@@ -17044,7 +16993,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D129" s="15">
         <v>1420</v>
@@ -17069,7 +17018,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D130" s="15">
         <v>1400</v>
@@ -17094,7 +17043,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D131" s="15">
         <v>1380</v>
@@ -17119,7 +17068,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D132" s="15">
         <v>1380</v>
@@ -17144,7 +17093,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D133" s="15">
         <v>1340</v>
@@ -17169,7 +17118,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D134" s="15">
         <v>1160</v>
@@ -17194,7 +17143,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D135" s="15">
         <v>1140</v>
@@ -17219,7 +17168,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D136" s="15">
         <v>1100</v>
@@ -17244,7 +17193,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D137" s="15">
         <v>1020</v>
@@ -17269,7 +17218,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D138" s="15">
         <v>1020</v>
@@ -17369,7 +17318,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D142" s="15">
         <v>0</v>
@@ -17419,7 +17368,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D144" s="15">
         <v>0</v>
@@ -17437,21 +17386,21 @@
     </row>
     <row r="145" spans="2:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B145" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C145" s="12"/>
       <c r="D145" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026[Points
+        <f>SUBTOTAL(109,AllianceMobilization202603[Points
 reached])</f>
         <v>286650</v>
       </c>
       <c r="E145" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202603[Quests
 started])</f>
         <v>1696</v>
       </c>
       <c r="F145" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202603[Quests
 completed])</f>
         <v>1698</v>
       </c>
@@ -17459,7 +17408,7 @@
     </row>
     <row r="146" spans="2:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="6">
@@ -17490,13 +17439,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D144">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17525,7 +17474,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -17537,7 +17486,7 @@
     </row>
     <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -17550,7 +17499,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17559,7 +17508,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17577,14 +17526,14 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -17596,12 +17545,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -17612,7 +17561,7 @@
     <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -17621,13 +17570,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -17639,7 +17588,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D13" s="14">
         <v>6820</v>
@@ -17664,7 +17613,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D14" s="14">
         <v>6200</v>
@@ -17689,7 +17638,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D15" s="14">
         <v>5400</v>
@@ -17714,7 +17663,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D16" s="14">
         <v>5380</v>
@@ -17739,7 +17688,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D17" s="14">
         <v>5340</v>
@@ -17764,7 +17713,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D18" s="14">
         <v>5260</v>
@@ -17789,7 +17738,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="D19" s="14">
         <v>5210</v>
@@ -17839,7 +17788,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14">
         <v>4660</v>
@@ -17914,7 +17863,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D24" s="14">
         <v>4100</v>
@@ -17939,7 +17888,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="14">
         <v>4040</v>
@@ -17964,7 +17913,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D26" s="14">
         <v>3940</v>
@@ -17989,7 +17938,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D27" s="14">
         <v>3820</v>
@@ -18014,7 +17963,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D28" s="14">
         <v>3720</v>
@@ -18089,7 +18038,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>379</v>
+        <v>263</v>
       </c>
       <c r="D31" s="14">
         <v>3490</v>
@@ -18164,7 +18113,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" s="14">
         <v>3170</v>
@@ -18189,7 +18138,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D35" s="14">
         <v>3150</v>
@@ -18214,7 +18163,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D36" s="14">
         <v>3140</v>
@@ -18239,7 +18188,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D37" s="14">
         <v>3140</v>
@@ -18264,7 +18213,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D38" s="14">
         <v>3040</v>
@@ -18314,7 +18263,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D40" s="14">
         <v>3000</v>
@@ -18339,7 +18288,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D41" s="14">
         <v>2990</v>
@@ -18364,7 +18313,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D42" s="14">
         <v>2940</v>
@@ -18439,7 +18388,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D45" s="14">
         <v>2750</v>
@@ -18464,7 +18413,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D46" s="14">
         <v>2740</v>
@@ -18489,7 +18438,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D47" s="14">
         <v>2730</v>
@@ -18514,7 +18463,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D48" s="14">
         <v>2720</v>
@@ -18564,7 +18513,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D50" s="14">
         <v>2680</v>
@@ -18589,7 +18538,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D51" s="14">
         <v>2670</v>
@@ -18614,7 +18563,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D52" s="14">
         <v>2670</v>
@@ -18664,7 +18613,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D54" s="14">
         <v>2660</v>
@@ -18689,7 +18638,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D55" s="14">
         <v>2610</v>
@@ -18714,7 +18663,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D56" s="14">
         <v>2600</v>
@@ -18739,7 +18688,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D57" s="14">
         <v>2600</v>
@@ -18764,7 +18713,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D58" s="14">
         <v>2570</v>
@@ -18789,7 +18738,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D59" s="14">
         <v>2540</v>
@@ -18814,7 +18763,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D60" s="14">
         <v>2520</v>
@@ -18864,7 +18813,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D62" s="14">
         <v>2520</v>
@@ -18889,7 +18838,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D63" s="14">
         <v>2500</v>
@@ -18914,7 +18863,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D64" s="14">
         <v>2480</v>
@@ -18939,7 +18888,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D65" s="14">
         <v>2460</v>
@@ -18964,7 +18913,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D66" s="14">
         <v>2440</v>
@@ -19039,7 +18988,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D69" s="14">
         <v>2380</v>
@@ -19064,7 +19013,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="D70" s="14">
         <v>2360</v>
@@ -19089,7 +19038,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D71" s="14">
         <v>2360</v>
@@ -19139,7 +19088,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D73" s="14">
         <v>2320</v>
@@ -19164,7 +19113,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D74" s="14">
         <v>2320</v>
@@ -19189,7 +19138,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D75" s="14">
         <v>2320</v>
@@ -19239,7 +19188,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D77" s="14">
         <v>2300</v>
@@ -19264,7 +19213,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D78" s="14">
         <v>2280</v>
@@ -19289,7 +19238,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D79" s="14">
         <v>2270</v>
@@ -19314,7 +19263,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D80" s="14">
         <v>2270</v>
@@ -19364,7 +19313,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D82" s="14">
         <v>2240</v>
@@ -19389,7 +19338,7 @@
         <v>71</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D83" s="14">
         <v>2220</v>
@@ -19414,7 +19363,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D84" s="14">
         <v>2180</v>
@@ -19439,7 +19388,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D85" s="14">
         <v>2180</v>
@@ -19464,7 +19413,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D86" s="14">
         <v>2160</v>
@@ -19489,7 +19438,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D87" s="14">
         <v>2160</v>
@@ -19514,7 +19463,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D88" s="14">
         <v>2150</v>
@@ -19539,7 +19488,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D89" s="14">
         <v>2100</v>
@@ -19564,7 +19513,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D90" s="14">
         <v>2090</v>
@@ -19589,7 +19538,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D91" s="14">
         <v>2080</v>
@@ -19614,7 +19563,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D92" s="14">
         <v>2080</v>
@@ -19664,7 +19613,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D94" s="14">
         <v>2080</v>
@@ -19689,7 +19638,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D95" s="14">
         <v>2080</v>
@@ -19714,7 +19663,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D96" s="14">
         <v>2070</v>
@@ -19739,7 +19688,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D97" s="14">
         <v>2060</v>
@@ -19764,7 +19713,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D98" s="14">
         <v>2060</v>
@@ -19789,7 +19738,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D99" s="14">
         <v>2060</v>
@@ -19814,7 +19763,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D100" s="14">
         <v>2050</v>
@@ -19839,7 +19788,7 @@
         <v>89</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D101" s="14">
         <v>2050</v>
@@ -19864,7 +19813,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D102" s="14">
         <v>2040</v>
@@ -19889,7 +19838,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D103" s="14">
         <v>2030</v>
@@ -19939,7 +19888,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D105" s="14">
         <v>2020</v>
@@ -19964,7 +19913,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D106" s="14">
         <v>2020</v>
@@ -19989,7 +19938,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D107" s="14">
         <v>2000</v>
@@ -20014,7 +19963,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D108" s="14">
         <v>2000</v>
@@ -20039,7 +19988,7 @@
         <v>97</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D109" s="14">
         <v>1920</v>
@@ -20064,7 +20013,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D110" s="14">
         <v>1900</v>
@@ -20089,7 +20038,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D111" s="14">
         <v>1870</v>
@@ -20139,7 +20088,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D113" s="14">
         <v>1750</v>
@@ -20164,7 +20113,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D114" s="14">
         <v>1740</v>
@@ -20189,7 +20138,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D115" s="14">
         <v>1660</v>
@@ -20214,7 +20163,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D116" s="14">
         <v>1660</v>
@@ -20239,7 +20188,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D117" s="14">
         <v>1540</v>
@@ -20289,7 +20238,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D119" s="14">
         <v>1460</v>
@@ -20314,7 +20263,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D120" s="14">
         <v>1410</v>
@@ -20339,7 +20288,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D121" s="14">
         <v>1320</v>
@@ -20364,7 +20313,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D122" s="14">
         <v>1320</v>
@@ -20389,7 +20338,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D123" s="14">
         <v>1060</v>
@@ -20414,7 +20363,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D124" s="14">
         <v>1060</v>
@@ -20439,7 +20388,7 @@
         <v>113</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D125" s="14">
         <v>930</v>
@@ -20464,7 +20413,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D126" s="14">
         <v>660</v>
@@ -20489,7 +20438,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D127" s="14">
         <v>260</v>
@@ -20514,7 +20463,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D128" s="14">
         <v>0</v>
@@ -20564,7 +20513,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D130" s="14">
         <v>0</v>
@@ -20589,7 +20538,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D131" s="14">
         <v>0</v>
@@ -20607,21 +20556,21 @@
     </row>
     <row r="132" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B132" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C132" s="12"/>
       <c r="D132" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026678[Points
+        <f>SUBTOTAL(109,AllianceMobilization202606[Points
 reached])</f>
         <v>303250</v>
       </c>
       <c r="E132" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026678[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202606[Quests
 started])</f>
         <v>1756</v>
       </c>
       <c r="F132" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch2026678[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202606[Quests
 completed])</f>
         <v>1758</v>
       </c>
@@ -20629,7 +20578,7 @@
     </row>
     <row r="133" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B133" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="6">
@@ -20660,13 +20609,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D131">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20695,7 +20644,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -20707,7 +20656,7 @@
     </row>
     <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -20720,7 +20669,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -20729,7 +20678,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -20747,14 +20696,14 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -20766,12 +20715,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -20782,7 +20731,7 @@
     <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -20791,13 +20740,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -20809,7 +20758,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D13" s="14">
         <v>6120</v>
@@ -20834,7 +20783,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D14" s="14">
         <v>5230</v>
@@ -20859,7 +20808,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D15" s="14">
         <v>4450</v>
@@ -20884,7 +20833,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D16" s="14">
         <v>4300</v>
@@ -20959,7 +20908,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D19" s="14">
         <v>3920</v>
@@ -21009,7 +20958,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D21" s="14">
         <v>3860</v>
@@ -21059,7 +21008,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" s="14">
         <v>3700</v>
@@ -21109,7 +21058,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D25" s="14">
         <v>3580</v>
@@ -21159,7 +21108,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D27" s="14">
         <v>3550</v>
@@ -21184,7 +21133,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D28" s="14">
         <v>3540</v>
@@ -21209,7 +21158,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D29" s="14">
         <v>3410</v>
@@ -21234,7 +21183,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D30" s="14">
         <v>3360</v>
@@ -21259,7 +21208,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D31" s="14">
         <v>3350</v>
@@ -21309,7 +21258,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D33" s="14">
         <v>3120</v>
@@ -21334,7 +21283,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D34" s="14">
         <v>3080</v>
@@ -21359,7 +21308,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D35" s="14">
         <v>3060</v>
@@ -21384,7 +21333,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="D36" s="14">
         <v>3060</v>
@@ -21459,7 +21408,7 @@
         <v>27</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D39" s="14">
         <v>2940</v>
@@ -21484,7 +21433,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D40" s="14">
         <v>2860</v>
@@ -21509,7 +21458,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D41" s="14">
         <v>2850</v>
@@ -21559,7 +21508,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D43" s="14">
         <v>2830</v>
@@ -21609,7 +21558,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D45" s="14">
         <v>2780</v>
@@ -21659,7 +21608,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D47" s="14">
         <v>2740</v>
@@ -21734,7 +21683,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D50" s="14">
         <v>2630</v>
@@ -21759,7 +21708,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D51" s="14">
         <v>2620</v>
@@ -21784,7 +21733,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D52" s="14">
         <v>2600</v>
@@ -21809,7 +21758,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D53" s="14">
         <v>2600</v>
@@ -21834,7 +21783,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D54" s="14">
         <v>2590</v>
@@ -21859,7 +21808,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D55" s="14">
         <v>2580</v>
@@ -21884,7 +21833,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D56" s="14">
         <v>2580</v>
@@ -21934,7 +21883,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D58" s="14">
         <v>2440</v>
@@ -21984,7 +21933,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D60" s="14">
         <v>2410</v>
@@ -22034,7 +21983,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D62" s="14">
         <v>2340</v>
@@ -22059,7 +22008,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D63" s="14">
         <v>2340</v>
@@ -22084,7 +22033,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D64" s="14">
         <v>2300</v>
@@ -22109,7 +22058,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D65" s="14">
         <v>2280</v>
@@ -22134,7 +22083,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D66" s="14">
         <v>2270</v>
@@ -22159,7 +22108,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D67" s="14">
         <v>2240</v>
@@ -22184,7 +22133,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D68" s="14">
         <v>2240</v>
@@ -22234,7 +22183,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D70" s="14">
         <v>2230</v>
@@ -22259,7 +22208,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D71" s="14">
         <v>2220</v>
@@ -22284,7 +22233,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="D72" s="14">
         <v>2200</v>
@@ -22309,7 +22258,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" s="14">
         <v>2200</v>
@@ -22359,7 +22308,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D75" s="14">
         <v>2140</v>
@@ -22384,7 +22333,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D76" s="14">
         <v>2130</v>
@@ -22409,7 +22358,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D77" s="14">
         <v>2120</v>
@@ -22459,7 +22408,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D79" s="14">
         <v>2080</v>
@@ -22484,7 +22433,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D80" s="14">
         <v>2070</v>
@@ -22509,7 +22458,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D81" s="14">
         <v>2060</v>
@@ -22559,7 +22508,7 @@
         <v>71</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D83" s="14">
         <v>2030</v>
@@ -22584,7 +22533,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D84" s="14">
         <v>2020</v>
@@ -22609,7 +22558,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D85" s="14">
         <v>2020</v>
@@ -22634,7 +22583,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D86" s="14">
         <v>1980</v>
@@ -22659,7 +22608,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D87" s="14">
         <v>1980</v>
@@ -22684,7 +22633,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="D88" s="14">
         <v>1970</v>
@@ -22709,7 +22658,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D89" s="14">
         <v>1970</v>
@@ -22734,7 +22683,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D90" s="14">
         <v>1970</v>
@@ -22759,7 +22708,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D91" s="14">
         <v>1940</v>
@@ -22784,7 +22733,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D92" s="14">
         <v>1930</v>
@@ -22809,7 +22758,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D93" s="14">
         <v>1930</v>
@@ -22834,7 +22783,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D94" s="14">
         <v>1920</v>
@@ -22859,7 +22808,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D95" s="14">
         <v>1920</v>
@@ -22884,7 +22833,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D96" s="14">
         <v>1920</v>
@@ -22934,7 +22883,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D98" s="14">
         <v>1900</v>
@@ -22959,7 +22908,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D99" s="14">
         <v>1870</v>
@@ -22984,7 +22933,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D100" s="14">
         <v>1870</v>
@@ -23034,7 +22983,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D102" s="14">
         <v>1860</v>
@@ -23059,7 +23008,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D103" s="14">
         <v>1840</v>
@@ -23084,20 +23033,20 @@
         <v>92</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="D104" s="14">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="E104" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F104" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="2"/>
-        <v>140.76923076923077</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23109,20 +23058,20 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="D105" s="14">
         <v>1820</v>
       </c>
       <c r="E105" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F105" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="2"/>
-        <v>182</v>
+        <v>165.45454545454547</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23134,20 +23083,20 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>344</v>
+        <v>167</v>
       </c>
       <c r="D106" s="14">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="E106" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F106" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="2"/>
-        <v>139.23076923076923</v>
+        <v>165.45454545454547</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23159,20 +23108,20 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="D107" s="14">
-        <v>1800</v>
+        <v>1820</v>
       </c>
       <c r="E107" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F107" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="2"/>
-        <v>138.46153846153845</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23184,20 +23133,20 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D108" s="14">
-        <v>1770</v>
+        <v>1810</v>
       </c>
       <c r="E108" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F108" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="2"/>
-        <v>160.90909090909091</v>
+        <v>150.83333333333334</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23209,20 +23158,20 @@
         <v>97</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>275</v>
+        <v>97</v>
       </c>
       <c r="D109" s="14">
-        <v>1740</v>
+        <v>1800</v>
       </c>
       <c r="E109" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F109" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="2"/>
-        <v>174</v>
+        <v>200</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23234,20 +23183,20 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="D110" s="14">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="E110" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F110" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="2"/>
-        <v>173</v>
+        <v>193.33333333333334</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23259,20 +23208,20 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>278</v>
+        <v>112</v>
       </c>
       <c r="D111" s="14">
         <v>1700</v>
       </c>
       <c r="E111" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F111" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="2"/>
-        <v>170</v>
+        <v>154.54545454545453</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23283,21 +23232,21 @@
       <c r="B112" s="14">
         <v>100</v>
       </c>
-      <c r="C112" s="13" t="s">
-        <v>356</v>
+      <c r="C112" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="D112" s="14">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="E112" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F112" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="2"/>
-        <v>137.5</v>
+        <v>150.90909090909091</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23309,20 +23258,20 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D113" s="14">
-        <v>1620</v>
+        <v>1510</v>
       </c>
       <c r="E113" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F113" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="2"/>
-        <v>147.27272727272728</v>
+        <v>125.83333333333333</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23334,20 +23283,20 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="D114" s="14">
-        <v>1610</v>
+        <v>1480</v>
       </c>
       <c r="E114" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F114" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="2"/>
-        <v>178.88888888888889</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23359,10 +23308,10 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D115" s="14">
-        <v>1600</v>
+        <v>1440</v>
       </c>
       <c r="E115" s="14">
         <v>9</v>
@@ -23372,7 +23321,7 @@
       </c>
       <c r="G115" s="15">
         <f t="shared" si="2"/>
-        <v>177.77777777777777</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23384,20 +23333,20 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="D116" s="14">
-        <v>1590</v>
+        <v>1420</v>
       </c>
       <c r="E116" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F116" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G116" s="15">
         <f t="shared" si="2"/>
-        <v>176.66666666666666</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23409,20 +23358,20 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>111</v>
+        <v>344</v>
       </c>
       <c r="D117" s="14">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="E117" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F117" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G117" s="15">
         <f t="shared" si="2"/>
-        <v>175</v>
+        <v>153.33333333333334</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -23434,7 +23383,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D118" s="14">
         <v>1200</v>
@@ -23459,7 +23408,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D119" s="14">
         <v>1100</v>
@@ -23484,7 +23433,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D120" s="14">
         <v>1040</v>
@@ -23509,7 +23458,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D121" s="14">
         <v>980</v>
@@ -23534,7 +23483,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D122" s="14">
         <v>920</v>
@@ -23559,7 +23508,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D123" s="14">
         <v>850</v>
@@ -23584,7 +23533,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D124" s="14">
         <v>850</v>
@@ -23634,7 +23583,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D126" s="14">
         <v>690</v>
@@ -23659,7 +23608,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D127" s="14">
         <v>660</v>
@@ -23684,7 +23633,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D128" s="14">
         <v>620</v>
@@ -23709,7 +23658,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D129" s="14">
         <v>560</v>
@@ -23734,7 +23683,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D130" s="14">
         <v>510</v>
@@ -23759,7 +23708,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D131" s="14">
         <v>480</v>
@@ -23784,7 +23733,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D132" s="14">
         <v>240</v>
@@ -23809,7 +23758,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D133" s="14">
         <v>240</v>
@@ -23834,7 +23783,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D134" s="14">
         <v>230</v>
@@ -23859,7 +23808,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D135" s="14">
         <v>200</v>
@@ -23909,7 +23858,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D137" s="14">
         <v>180</v>
@@ -23934,7 +23883,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D138" s="14">
         <v>150</v>
@@ -23959,7 +23908,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -23984,7 +23933,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D140" s="14">
         <v>0</v>
@@ -24009,7 +23958,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D141" s="14">
         <v>0</v>
@@ -24034,7 +23983,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D142" s="14">
         <v>0</v>
@@ -24059,7 +24008,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -24084,7 +24033,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -24109,7 +24058,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -24134,7 +24083,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D146" s="14">
         <v>0</v>
@@ -24159,7 +24108,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D147" s="14">
         <v>0</v>
@@ -24184,7 +24133,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D148" s="14">
         <v>0</v>
@@ -24209,7 +24158,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D149" s="14">
         <v>0</v>
@@ -24234,7 +24183,7 @@
         <v>138</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D150" s="14">
         <v>0</v>
@@ -24259,7 +24208,7 @@
         <v>139</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D151" s="14">
         <v>0</v>
@@ -24284,7 +24233,7 @@
         <v>140</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D152" s="14">
         <v>0</v>
@@ -24302,46 +24251,46 @@
     </row>
     <row r="153" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B153" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C153" s="12"/>
       <c r="D153" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202667[Points
+        <f>SUBTOTAL(109,AllianceMobilization202607[Points
 reached])</f>
-        <v>281230</v>
+        <v>280800</v>
       </c>
       <c r="E153" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202667[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202607[Quests
 started])</f>
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="F153" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202667[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202607[Quests
 completed])</f>
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="G153" s="16"/>
     </row>
     <row r="154" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B154" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C154" s="5"/>
       <c r="D154" s="6">
         <f>AVERAGE(D13:D152)</f>
-        <v>2008.7857142857142</v>
+        <v>2005.7142857142858</v>
       </c>
       <c r="E154" s="6">
         <f>AVERAGE(E13:E152)</f>
-        <v>11.478571428571428</v>
+        <v>11.435714285714285</v>
       </c>
       <c r="F154" s="6">
         <f>AVERAGE(F13:F152)</f>
-        <v>11.478571428571428</v>
+        <v>11.435714285714285</v>
       </c>
       <c r="G154" s="6">
         <f>AVERAGE(G13:G152)</f>
-        <v>155.48438354976392</v>
+        <v>155.76809983348014</v>
       </c>
     </row>
   </sheetData>
@@ -24355,13 +24304,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D152">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24390,7 +24339,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -24402,7 +24351,7 @@
     </row>
     <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -24415,7 +24364,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -24424,7 +24373,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -24442,14 +24391,14 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -24461,12 +24410,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -24477,7 +24426,7 @@
     <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -24486,13 +24435,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -24504,7 +24453,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D13" s="14">
         <v>6500</v>
@@ -24529,7 +24478,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D14" s="14">
         <v>5280</v>
@@ -24554,7 +24503,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D15" s="14">
         <v>5020</v>
@@ -24579,7 +24528,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D16" s="14">
         <v>4830</v>
@@ -24629,7 +24578,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="14">
         <v>4210</v>
@@ -24704,7 +24653,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14">
         <v>4060</v>
@@ -24729,7 +24678,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D22" s="14">
         <v>3840</v>
@@ -24804,7 +24753,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D25" s="14">
         <v>3400</v>
@@ -24829,7 +24778,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D26" s="14">
         <v>3340</v>
@@ -24854,7 +24803,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D27" s="14">
         <v>3340</v>
@@ -24879,7 +24828,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D28" s="14">
         <v>3260</v>
@@ -24904,7 +24853,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D29" s="14">
         <v>3140</v>
@@ -24979,7 +24928,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D32" s="14">
         <v>2960</v>
@@ -25004,7 +24953,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D33" s="14">
         <v>2940</v>
@@ -25054,7 +25003,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D35" s="14">
         <v>2850</v>
@@ -25079,7 +25028,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" s="14">
         <v>2810</v>
@@ -25104,7 +25053,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D37" s="14">
         <v>2800</v>
@@ -25179,7 +25128,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D40" s="14">
         <v>2770</v>
@@ -25204,7 +25153,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D41" s="14">
         <v>2750</v>
@@ -25229,7 +25178,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D42" s="14">
         <v>2730</v>
@@ -25254,7 +25203,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D43" s="14">
         <v>2660</v>
@@ -25279,7 +25228,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D44" s="14">
         <v>2640</v>
@@ -25304,7 +25253,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D45" s="14">
         <v>2640</v>
@@ -25354,7 +25303,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D47" s="14">
         <v>2620</v>
@@ -25379,7 +25328,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D48" s="14">
         <v>2580</v>
@@ -25479,7 +25428,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D52" s="14">
         <v>2480</v>
@@ -25504,7 +25453,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" s="14">
         <v>2450</v>
@@ -25529,7 +25478,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D54" s="14">
         <v>2440</v>
@@ -25554,7 +25503,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D55" s="14">
         <v>2420</v>
@@ -25579,7 +25528,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D56" s="14">
         <v>2420</v>
@@ -25604,7 +25553,7 @@
         <v>45</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D57" s="14">
         <v>2390</v>
@@ -25629,7 +25578,7 @@
         <v>46</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D58" s="14">
         <v>2380</v>
@@ -25654,7 +25603,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D59" s="14">
         <v>2380</v>
@@ -25679,7 +25628,7 @@
         <v>48</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D60" s="14">
         <v>2380</v>
@@ -25704,7 +25653,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D61" s="14">
         <v>2370</v>
@@ -25729,7 +25678,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D62" s="14">
         <v>2360</v>
@@ -25754,7 +25703,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D63" s="14">
         <v>2340</v>
@@ -25779,7 +25728,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D64" s="14">
         <v>2240</v>
@@ -25804,7 +25753,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D65" s="14">
         <v>2240</v>
@@ -25829,7 +25778,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D66" s="14">
         <v>2220</v>
@@ -25854,7 +25803,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D67" s="14">
         <v>2200</v>
@@ -25879,7 +25828,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D68" s="14">
         <v>2190</v>
@@ -25904,7 +25853,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D69" s="14">
         <v>2180</v>
@@ -25954,7 +25903,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D71" s="14">
         <v>2160</v>
@@ -26004,7 +25953,7 @@
         <v>61</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D73" s="14">
         <v>2120</v>
@@ -26029,7 +25978,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D74" s="14">
         <v>2120</v>
@@ -26054,7 +26003,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D75" s="14">
         <v>2110</v>
@@ -26079,7 +26028,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D76" s="14">
         <v>2100</v>
@@ -26129,7 +26078,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D78" s="14">
         <v>2080</v>
@@ -26154,7 +26103,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D79" s="14">
         <v>2070</v>
@@ -26179,7 +26128,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D80" s="14">
         <v>2040</v>
@@ -26204,7 +26153,7 @@
         <v>69</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D81" s="14">
         <v>2040</v>
@@ -26229,7 +26178,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D82" s="14">
         <v>2040</v>
@@ -26279,7 +26228,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D84" s="14">
         <v>2020</v>
@@ -26304,7 +26253,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D85" s="14">
         <v>2020</v>
@@ -26329,7 +26278,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D86" s="14">
         <v>2010</v>
@@ -26354,7 +26303,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D87" s="14">
         <v>2000</v>
@@ -26379,7 +26328,7 @@
         <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D88" s="14">
         <v>2000</v>
@@ -26404,7 +26353,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D89" s="14">
         <v>1990</v>
@@ -26429,7 +26378,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D90" s="14">
         <v>1960</v>
@@ -26479,7 +26428,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D92" s="14">
         <v>1920</v>
@@ -26504,7 +26453,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D93" s="14">
         <v>1920</v>
@@ -26529,7 +26478,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D94" s="14">
         <v>1910</v>
@@ -26554,7 +26503,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D95" s="14">
         <v>1890</v>
@@ -26579,7 +26528,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D96" s="14">
         <v>1890</v>
@@ -26604,7 +26553,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D97" s="14">
         <v>1880</v>
@@ -26629,7 +26578,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D98" s="14">
         <v>1880</v>
@@ -26654,7 +26603,7 @@
         <v>87</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D99" s="14">
         <v>1860</v>
@@ -26679,7 +26628,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D100" s="14">
         <v>1850</v>
@@ -26704,7 +26653,7 @@
         <v>89</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D101" s="14">
         <v>1840</v>
@@ -26729,7 +26678,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D102" s="14">
         <v>1820</v>
@@ -26754,7 +26703,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D103" s="14">
         <v>1820</v>
@@ -26779,7 +26728,7 @@
         <v>92</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D104" s="14">
         <v>1820</v>
@@ -26804,7 +26753,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D105" s="14">
         <v>1800</v>
@@ -26829,7 +26778,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D106" s="14">
         <v>1800</v>
@@ -26879,7 +26828,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D108" s="14">
         <v>1770</v>
@@ -26929,7 +26878,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D110" s="14">
         <v>1700</v>
@@ -26954,7 +26903,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D111" s="14">
         <v>1530</v>
@@ -26979,7 +26928,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D112" s="14">
         <v>1510</v>
@@ -27004,7 +26953,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>300</v>
+        <v>383</v>
       </c>
       <c r="D113" s="14">
         <v>1480</v>
@@ -27029,7 +26978,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D114" s="14">
         <v>1270</v>
@@ -27054,7 +27003,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D115" s="14">
         <v>1180</v>
@@ -27079,7 +27028,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D116" s="14">
         <v>1180</v>
@@ -27104,7 +27053,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="D117" s="14">
         <v>1140</v>
@@ -27129,7 +27078,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D118" s="14">
         <v>1130</v>
@@ -27154,7 +27103,7 @@
         <v>107</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D119" s="14">
         <v>1100</v>
@@ -27204,7 +27153,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D121" s="14">
         <v>920</v>
@@ -27229,7 +27178,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D122" s="14">
         <v>840</v>
@@ -27254,7 +27203,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D123" s="14">
         <v>810</v>
@@ -27279,7 +27228,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D124" s="14">
         <v>760</v>
@@ -27329,7 +27278,7 @@
         <v>114</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D126" s="14">
         <v>360</v>
@@ -27354,7 +27303,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D127" s="14">
         <v>360</v>
@@ -27379,7 +27328,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D128" s="14">
         <v>220</v>
@@ -27404,7 +27353,7 @@
         <v>117</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D129" s="14">
         <v>180</v>
@@ -27429,7 +27378,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D130" s="14">
         <v>180</v>
@@ -27454,7 +27403,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D131" s="14">
         <v>180</v>
@@ -27479,7 +27428,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D132" s="14">
         <v>60</v>
@@ -27504,7 +27453,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D133" s="14">
         <v>0</v>
@@ -27529,7 +27478,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D134" s="14">
         <v>0</v>
@@ -27554,7 +27503,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D135" s="14">
         <v>0</v>
@@ -27579,7 +27528,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D136" s="14">
         <v>0</v>
@@ -27629,7 +27578,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D138" s="14">
         <v>0</v>
@@ -27654,7 +27603,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -27679,7 +27628,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D140" s="14">
         <v>0</v>
@@ -27704,7 +27653,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D141" s="14">
         <v>0</v>
@@ -27729,7 +27678,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D142" s="14">
         <v>0</v>
@@ -27754,7 +27703,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -27779,7 +27728,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -27804,7 +27753,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -27829,7 +27778,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="D146" s="14">
         <v>0</v>
@@ -27854,7 +27803,7 @@
         <v>135</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D147" s="14">
         <v>0</v>
@@ -27879,7 +27828,7 @@
         <v>136</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D148" s="14">
         <v>0</v>
@@ -27904,7 +27853,7 @@
         <v>137</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D149" s="14">
         <v>0</v>
@@ -27922,21 +27871,21 @@
     </row>
     <row r="150" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B150" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C150" s="12"/>
       <c r="D150" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch20266[Points
+        <f>SUBTOTAL(109,AllianceMobilization202608[Points
 reached])</f>
         <v>271150</v>
       </c>
       <c r="E150" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch20266[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202608[Quests
 started])</f>
         <v>1545</v>
       </c>
       <c r="F150" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch20266[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202608[Quests
 completed])</f>
         <v>1545</v>
       </c>
@@ -27944,7 +27893,7 @@
     </row>
     <row r="151" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B151" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C151" s="5"/>
       <c r="D151" s="6">
@@ -27975,13 +27924,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D149">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28010,7 +27959,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -28022,7 +27971,7 @@
     </row>
     <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="20" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="19">
@@ -28035,7 +27984,7 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="10" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28044,7 +27993,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="10" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28062,14 +28011,14 @@
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D8" s="11">
         <v>18</v>
@@ -28081,12 +28030,12 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="10" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="11">
@@ -28097,7 +28046,7 @@
     <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>9</v>
@@ -28106,13 +28055,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -28124,7 +28073,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" s="14">
         <v>5880</v>
@@ -28149,7 +28098,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D14" s="14">
         <v>4950</v>
@@ -28174,7 +28123,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D15" s="14">
         <v>4740</v>
@@ -28199,7 +28148,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="14">
         <v>4520</v>
@@ -28224,7 +28173,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D17" s="14">
         <v>4300</v>
@@ -28249,7 +28198,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D18" s="14">
         <v>4200</v>
@@ -28274,7 +28223,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D19" s="14">
         <v>4020</v>
@@ -28299,7 +28248,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="D20" s="14">
         <v>3980</v>
@@ -28324,7 +28273,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D21" s="14">
         <v>3780</v>
@@ -28349,7 +28298,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D22" s="14">
         <v>3710</v>
@@ -28374,7 +28323,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="D23" s="14">
         <v>3650</v>
@@ -28449,7 +28398,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D26" s="14">
         <v>3460</v>
@@ -28499,7 +28448,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D28" s="14">
         <v>3360</v>
@@ -28524,7 +28473,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D29" s="14">
         <v>3320</v>
@@ -28599,7 +28548,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D32" s="14">
         <v>3120</v>
@@ -28624,7 +28573,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D33" s="14">
         <v>3060</v>
@@ -28649,7 +28598,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" s="14">
         <v>3040</v>
@@ -28674,7 +28623,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D35" s="14">
         <v>2940</v>
@@ -28724,7 +28673,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D37" s="14">
         <v>2860</v>
@@ -28749,7 +28698,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D38" s="14">
         <v>2810</v>
@@ -28799,7 +28748,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D40" s="14">
         <v>2720</v>
@@ -28824,7 +28773,7 @@
         <v>29</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D41" s="14">
         <v>2680</v>
@@ -28849,7 +28798,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D42" s="14">
         <v>2660</v>
@@ -28899,7 +28848,7 @@
         <v>32</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D44" s="14">
         <v>2640</v>
@@ -28924,7 +28873,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D45" s="14">
         <v>2610</v>
@@ -28949,7 +28898,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D46" s="14">
         <v>2600</v>
@@ -28999,7 +28948,7 @@
         <v>36</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D48" s="14">
         <v>2550</v>
@@ -29049,7 +28998,7 @@
         <v>38</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D50" s="14">
         <v>2540</v>
@@ -29099,7 +29048,7 @@
         <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D52" s="14">
         <v>2490</v>
@@ -29124,7 +29073,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D53" s="14">
         <v>2460</v>
@@ -29149,7 +29098,7 @@
         <v>42</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D54" s="14">
         <v>2460</v>
@@ -29174,7 +29123,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55" s="14">
         <v>2430</v>
@@ -29199,7 +29148,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D56" s="14">
         <v>2420</v>
@@ -29274,7 +29223,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D59" s="14">
         <v>2400</v>
@@ -29324,7 +29273,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D61" s="14">
         <v>2360</v>
@@ -29349,7 +29298,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D62" s="14">
         <v>2360</v>
@@ -29374,7 +29323,7 @@
         <v>51</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D63" s="14">
         <v>2340</v>
@@ -29399,7 +29348,7 @@
         <v>52</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D64" s="14">
         <v>2330</v>
@@ -29424,7 +29373,7 @@
         <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D65" s="14">
         <v>2300</v>
@@ -29449,7 +29398,7 @@
         <v>54</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D66" s="14">
         <v>2290</v>
@@ -29474,7 +29423,7 @@
         <v>55</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D67" s="14">
         <v>2280</v>
@@ -29499,7 +29448,7 @@
         <v>56</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D68" s="14">
         <v>2220</v>
@@ -29524,7 +29473,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="D69" s="14">
         <v>2190</v>
@@ -29549,7 +29498,7 @@
         <v>58</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D70" s="14">
         <v>2150</v>
@@ -29574,7 +29523,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D71" s="14">
         <v>2140</v>
@@ -29599,7 +29548,7 @@
         <v>60</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D72" s="14">
         <v>2140</v>
@@ -29649,7 +29598,7 @@
         <v>62</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D74" s="14">
         <v>2140</v>
@@ -29699,7 +29648,7 @@
         <v>64</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D76" s="14">
         <v>2130</v>
@@ -29724,7 +29673,7 @@
         <v>65</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D77" s="14">
         <v>2120</v>
@@ -29749,7 +29698,7 @@
         <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D78" s="14">
         <v>2120</v>
@@ -29774,7 +29723,7 @@
         <v>67</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D79" s="14">
         <v>2100</v>
@@ -29799,7 +29748,7 @@
         <v>68</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D80" s="14">
         <v>2060</v>
@@ -29849,7 +29798,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D82" s="14">
         <v>2050</v>
@@ -29874,7 +29823,7 @@
         <v>71</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D83" s="14">
         <v>2050</v>
@@ -29899,7 +29848,7 @@
         <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D84" s="14">
         <v>2050</v>
@@ -29924,7 +29873,7 @@
         <v>73</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D85" s="14">
         <v>2040</v>
@@ -29974,7 +29923,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D87" s="14">
         <v>2040</v>
@@ -30024,7 +29973,7 @@
         <v>77</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D89" s="14">
         <v>2000</v>
@@ -30049,7 +29998,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D90" s="14">
         <v>2000</v>
@@ -30074,7 +30023,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D91" s="14">
         <v>1960</v>
@@ -30099,7 +30048,7 @@
         <v>80</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D92" s="14">
         <v>1950</v>
@@ -30124,7 +30073,7 @@
         <v>81</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D93" s="14">
         <v>1920</v>
@@ -30149,7 +30098,7 @@
         <v>82</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D94" s="14">
         <v>1920</v>
@@ -30174,7 +30123,7 @@
         <v>83</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D95" s="14">
         <v>1900</v>
@@ -30199,7 +30148,7 @@
         <v>84</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D96" s="14">
         <v>1880</v>
@@ -30224,7 +30173,7 @@
         <v>85</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D97" s="14">
         <v>1840</v>
@@ -30249,7 +30198,7 @@
         <v>86</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D98" s="14">
         <v>1840</v>
@@ -30299,7 +30248,7 @@
         <v>88</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D100" s="14">
         <v>1660</v>
@@ -30324,7 +30273,7 @@
         <v>89</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D101" s="14">
         <v>1640</v>
@@ -30349,7 +30298,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D102" s="14">
         <v>1620</v>
@@ -30374,7 +30323,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D103" s="14">
         <v>1540</v>
@@ -30399,7 +30348,7 @@
         <v>92</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D104" s="14">
         <v>1520</v>
@@ -30424,7 +30373,7 @@
         <v>93</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D105" s="14">
         <v>1460</v>
@@ -30449,7 +30398,7 @@
         <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D106" s="14">
         <v>1460</v>
@@ -30474,7 +30423,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D107" s="14">
         <v>1400</v>
@@ -30499,7 +30448,7 @@
         <v>96</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D108" s="14">
         <v>1360</v>
@@ -30549,7 +30498,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D110" s="14">
         <v>1300</v>
@@ -30574,7 +30523,7 @@
         <v>99</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D111" s="14">
         <v>1260</v>
@@ -30599,7 +30548,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D112" s="14">
         <v>1220</v>
@@ -30624,7 +30573,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D113" s="14">
         <v>1160</v>
@@ -30649,7 +30598,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D114" s="14">
         <v>1080</v>
@@ -30674,7 +30623,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D115" s="14">
         <v>1030</v>
@@ -30699,7 +30648,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D116" s="14">
         <v>1000</v>
@@ -30724,7 +30673,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D117" s="14">
         <v>960</v>
@@ -30749,7 +30698,7 @@
         <v>106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D118" s="14">
         <v>910</v>
@@ -30799,7 +30748,7 @@
         <v>108</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D120" s="14">
         <v>890</v>
@@ -30824,7 +30773,7 @@
         <v>109</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="D121" s="14">
         <v>860</v>
@@ -30849,7 +30798,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D122" s="14">
         <v>840</v>
@@ -30874,7 +30823,7 @@
         <v>111</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D123" s="14">
         <v>820</v>
@@ -30899,7 +30848,7 @@
         <v>112</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D124" s="14">
         <v>770</v>
@@ -30924,7 +30873,7 @@
         <v>113</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D125" s="14">
         <v>720</v>
@@ -30974,7 +30923,7 @@
         <v>115</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D127" s="14">
         <v>620</v>
@@ -30999,7 +30948,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D128" s="14">
         <v>600</v>
@@ -31049,7 +30998,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D130" s="14">
         <v>470</v>
@@ -31074,7 +31023,7 @@
         <v>119</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D131" s="14">
         <v>360</v>
@@ -31099,7 +31048,7 @@
         <v>120</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D132" s="14">
         <v>230</v>
@@ -31124,7 +31073,7 @@
         <v>121</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D133" s="14">
         <v>220</v>
@@ -31149,7 +31098,7 @@
         <v>122</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D134" s="14">
         <v>0</v>
@@ -31174,7 +31123,7 @@
         <v>123</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D135" s="14">
         <v>0</v>
@@ -31199,7 +31148,7 @@
         <v>124</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D136" s="14">
         <v>0</v>
@@ -31224,7 +31173,7 @@
         <v>125</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D137" s="14">
         <v>0</v>
@@ -31249,7 +31198,7 @@
         <v>126</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D138" s="14">
         <v>0</v>
@@ -31274,7 +31223,7 @@
         <v>127</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="D139" s="14">
         <v>0</v>
@@ -31299,7 +31248,7 @@
         <v>128</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D140" s="14">
         <v>0</v>
@@ -31324,7 +31273,7 @@
         <v>129</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D141" s="14">
         <v>0</v>
@@ -31349,7 +31298,7 @@
         <v>130</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D142" s="14">
         <v>0</v>
@@ -31374,7 +31323,7 @@
         <v>131</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D143" s="14">
         <v>0</v>
@@ -31399,7 +31348,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D144" s="14">
         <v>0</v>
@@ -31424,7 +31373,7 @@
         <v>133</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="D145" s="14">
         <v>0</v>
@@ -31449,7 +31398,7 @@
         <v>134</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D146" s="14">
         <v>0</v>
@@ -31467,21 +31416,21 @@
     </row>
     <row r="147" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C147" s="12"/>
       <c r="D147" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202669[Points
+        <f>SUBTOTAL(109,AllianceMobilization202609[Points
 reached])</f>
         <v>267440</v>
       </c>
       <c r="E147" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202669[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202609[Quests
 started])</f>
         <v>1526</v>
       </c>
       <c r="F147" s="15">
-        <f>SUBTOTAL(109,AllianceMobilizationMarch202669[Quests
+        <f>SUBTOTAL(109,AllianceMobilization202609[Quests
 completed])</f>
         <v>1526</v>
       </c>
@@ -31489,7 +31438,7 @@
     </row>
     <row r="148" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B148" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="6">
@@ -31520,13 +31469,13 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:D146">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>$D$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>$D$10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31537,4 +31486,285 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E19C7A-C31C-444C-9763-F2B307F2A8B3}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.6328125" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+    <col min="3" max="3" width="32.6328125" style="21" customWidth="1"/>
+    <col min="4" max="5" width="32.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="21" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="19">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" s="22" t="str">
+        <f>"November 2025"</f>
+        <v>November 2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C5" s="22" t="str">
+        <f>"September 2026"</f>
+        <v>September 2026</v>
+      </c>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <f>ROW(A1)</f>
+        <v>1</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <f>ROW(A2)</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <f>ROW(A3)</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <f t="shared" ref="A10:A21" si="0">ROW(A6)</f>
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" spans="1:5" s="21" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>